--- a/Trabajo/E-commerce/Amazon/AVIE/AVIE_OCT_bulk_carga.xlsx
+++ b/Trabajo/E-commerce/Amazon/AVIE/AVIE_OCT_bulk_carga.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA260"/>
+  <dimension ref="A1:AA302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1910,51 +1910,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AVIE_OCT_QUICKWIN_EX</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>AVIE_OCT_PROBADAS_EX</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>avie_oct_probadas_ex</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>AVIE_OCT_QUICKWIN_EX</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P23" t="n">
-        <v>8</v>
-      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>lymphatic contour face brush</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Dynamic bids - down only</t>
-        </is>
-      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
@@ -1967,7 +1965,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1980,40 +1978,48 @@
           <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>avie_oct_quickwin_ex</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>avie_oct_quickwin_ex</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>7</v>
+      </c>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="n">
-        <v>0.75</v>
-      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
+        </is>
+      </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
@@ -2026,7 +2032,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2049,7 +2055,11 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>avie_oct_quickwin_ex</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -2059,12 +2069,10 @@
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>avie 011</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>0.75</v>
+      </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
@@ -2083,7 +2091,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2116,25 +2124,17 @@
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>avie 011</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>skin brush for face</t>
-        </is>
-      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
+      <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>soft guasha facial brush</t>
+          <t>skin brush for face</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>depuffing brush for face</t>
+          <t>soft guasha facial brush</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>brush for face drainage</t>
+          <t>depuffing brush for face</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush soft bristles</t>
+          <t>brush for face drainage</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>lymphatic drainage brush soft</t>
+          <t>lymphatic contour face brush soft bristles</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>face drainage brush</t>
+          <t>lymphatic drainage brush soft</t>
         </is>
       </c>
       <c r="U32" t="inlineStr"/>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>de-bloat face sculpting brush</t>
+          <t>face drainage brush</t>
         </is>
       </c>
       <c r="U33" t="inlineStr"/>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>gua sha dry brush</t>
+          <t>de-bloat face sculpting brush</t>
         </is>
       </c>
       <c r="U34" t="inlineStr"/>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>face brush gua sha</t>
+          <t>gua sha dry brush</t>
         </is>
       </c>
       <c r="U35" t="inlineStr"/>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>gua sha face brush</t>
+          <t>face brush gua sha</t>
         </is>
       </c>
       <c r="U36" t="inlineStr"/>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush korean</t>
+          <t>gua sha face brush</t>
         </is>
       </c>
       <c r="U37" t="inlineStr"/>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>guasha face brush</t>
+          <t>lymphatic contour face brush korean</t>
         </is>
       </c>
       <c r="U38" t="inlineStr"/>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>face brushes for lymphatic drainage</t>
+          <t>guasha face brush</t>
         </is>
       </c>
       <c r="U39" t="inlineStr"/>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>brush guasha for face</t>
+          <t>face brushes for lymphatic drainage</t>
         </is>
       </c>
       <c r="U40" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>lymphatic drainage brush face</t>
+          <t>brush guasha for face</t>
         </is>
       </c>
       <c r="U41" t="inlineStr"/>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>gua sha facial brush</t>
+          <t>lymphatic drainage brush face</t>
         </is>
       </c>
       <c r="U42" t="inlineStr"/>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>lymphatic facial drainage brush</t>
+          <t>gua sha facial brush</t>
         </is>
       </c>
       <c r="U43" t="inlineStr"/>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>face gua sha brush</t>
+          <t>lymphatic facial drainage brush</t>
         </is>
       </c>
       <c r="U44" t="inlineStr"/>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>contour facial brush</t>
+          <t>face gua sha brush</t>
         </is>
       </c>
       <c r="U45" t="inlineStr"/>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>contour brush lymphatic drainage</t>
+          <t>contour facial brush</t>
         </is>
       </c>
       <c r="U46" t="inlineStr"/>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>facial contour brush lymphatic</t>
+          <t>contour brush lymphatic drainage</t>
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>lymphatic beauty brush</t>
+          <t>facial contour brush lymphatic</t>
         </is>
       </c>
       <c r="U48" t="inlineStr"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>gua sha dry brush for face</t>
+          <t>lymphatic beauty brush</t>
         </is>
       </c>
       <c r="U49" t="inlineStr"/>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>facial sculpting brushes for lymphatic drainage</t>
+          <t>gua sha dry brush for face</t>
         </is>
       </c>
       <c r="U50" t="inlineStr"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>lymphatic drainage facial brush</t>
+          <t>facial sculpting brushes for lymphatic drainage</t>
         </is>
       </c>
       <c r="U51" t="inlineStr"/>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush soft</t>
+          <t>lymphatic drainage facial brush</t>
         </is>
       </c>
       <c r="U52" t="inlineStr"/>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>lymphatic drain face brush</t>
+          <t>lymphatic contour face brush soft</t>
         </is>
       </c>
       <c r="U53" t="inlineStr"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>facial sculpting brush</t>
+          <t>lymphatic drain face brush</t>
         </is>
       </c>
       <c r="U54" t="inlineStr"/>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>soft face brush lymphatic</t>
+          <t>facial sculpting brush</t>
         </is>
       </c>
       <c r="U55" t="inlineStr"/>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>lymphatic drain brush for face</t>
+          <t>soft face brush lymphatic</t>
         </is>
       </c>
       <c r="U56" t="inlineStr"/>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>facial brushes for lymphatic drainage</t>
+          <t>lymphatic drain brush for face</t>
         </is>
       </c>
       <c r="U57" t="inlineStr"/>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>lymphatic draining brush for face</t>
+          <t>facial brushes for lymphatic drainage</t>
         </is>
       </c>
       <c r="U58" t="inlineStr"/>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>facial drainage brush</t>
+          <t>lymphatic draining brush for face</t>
         </is>
       </c>
       <c r="U59" t="inlineStr"/>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>sculpt brush for face</t>
+          <t>facial drainage brush</t>
         </is>
       </c>
       <c r="U60" t="inlineStr"/>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>korean face lifting brush</t>
+          <t>sculpt brush for face</t>
         </is>
       </c>
       <c r="U61" t="inlineStr"/>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>facial lymph drainage brush</t>
+          <t>korean face lifting brush</t>
         </is>
       </c>
       <c r="U62" t="inlineStr"/>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>lymphatic facial contour brush</t>
+          <t>facial lymph drainage brush</t>
         </is>
       </c>
       <c r="U63" t="inlineStr"/>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>sculpting face brush</t>
+          <t>lymphatic facial contour brush</t>
         </is>
       </c>
       <c r="U64" t="inlineStr"/>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>dry lymphatic massage brush for face</t>
+          <t>sculpting face brush</t>
         </is>
       </c>
       <c r="U65" t="inlineStr"/>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>lymphatic contour brush for face</t>
+          <t>dry lymphatic massage brush for face</t>
         </is>
       </c>
       <c r="U66" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>face brush lymphatic drainage</t>
+          <t>lymphatic contour brush for face</t>
         </is>
       </c>
       <c r="U67" t="inlineStr"/>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>facial contour brush</t>
+          <t>face brush lymphatic drainage</t>
         </is>
       </c>
       <c r="U68" t="inlineStr"/>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>contour lymphatic face brush</t>
+          <t>facial contour brush</t>
         </is>
       </c>
       <c r="U69" t="inlineStr"/>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>dry brush face</t>
+          <t>contour lymphatic face brush</t>
         </is>
       </c>
       <c r="U70" t="inlineStr"/>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>face lymphatic brush</t>
+          <t>dry brush face</t>
         </is>
       </c>
       <c r="U71" t="inlineStr"/>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>korean brush for face</t>
+          <t>face lymphatic brush</t>
         </is>
       </c>
       <c r="U72" t="inlineStr"/>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>face lymphatic contour brush</t>
+          <t>korean brush for face</t>
         </is>
       </c>
       <c r="U73" t="inlineStr"/>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>face massage brush</t>
+          <t>face lymphatic contour brush</t>
         </is>
       </c>
       <c r="U74" t="inlineStr"/>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>dry brush for lymphatic drainage face</t>
+          <t>face massage brush</t>
         </is>
       </c>
       <c r="U75" t="inlineStr"/>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>face lifting brush</t>
+          <t>dry brush for lymphatic drainage face</t>
         </is>
       </c>
       <c r="U76" t="inlineStr"/>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>depuff brush for face</t>
+          <t>face lifting brush</t>
         </is>
       </c>
       <c r="U77" t="inlineStr"/>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>face dry brush for lymphatic drainage</t>
+          <t>depuff brush for face</t>
         </is>
       </c>
       <c r="U78" t="inlineStr"/>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>korean lymphatic face brush</t>
+          <t>face dry brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U79" t="inlineStr"/>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5603,51 +5603,49 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>avie_oct_quickwin_ex</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
-        </is>
-      </c>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
+      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P80" t="n">
-        <v>3</v>
-      </c>
+      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>korean lymphatic face brush</t>
+        </is>
+      </c>
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>Dynamic bids - down only</t>
-        </is>
-      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr"/>
@@ -5660,7 +5658,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5670,12 +5668,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -5683,11 +5681,7 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>avie_oct_rivales_ex</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
@@ -5698,14 +5692,24 @@
       </c>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>glow brush lymphatic</t>
+        </is>
+      </c>
       <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr"/>
@@ -5719,7 +5723,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5729,12 +5733,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -5752,17 +5756,25 @@
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>avie 011</t>
-        </is>
-      </c>
+      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>korean lymphatic brush</t>
+        </is>
+      </c>
       <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
@@ -5786,12 +5798,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -5813,12 +5825,12 @@
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>contour glow brush for face</t>
+          <t>glow brush for face</t>
         </is>
       </c>
       <c r="U83" t="inlineStr"/>
@@ -5851,12 +5863,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -5878,12 +5890,12 @@
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>k glow face sculpting brush</t>
+          <t>counter glow face brush</t>
         </is>
       </c>
       <c r="U84" t="inlineStr"/>
@@ -5916,12 +5928,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -5943,12 +5955,12 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>contour glow brush</t>
+          <t>counterglow face brush</t>
         </is>
       </c>
       <c r="U85" t="inlineStr"/>
@@ -5981,12 +5993,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -6008,12 +6020,12 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush k glow</t>
+          <t>face massager brush</t>
         </is>
       </c>
       <c r="U86" t="inlineStr"/>
@@ -6046,12 +6058,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -6073,12 +6085,12 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>contour glow face brush</t>
+          <t>contour face brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U87" t="inlineStr"/>
@@ -6111,12 +6123,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -6138,12 +6150,12 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>contourglow brush</t>
+          <t>lymphatic drainage face brush</t>
         </is>
       </c>
       <c r="U88" t="inlineStr"/>
@@ -6176,12 +6188,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -6203,12 +6215,12 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>skinn double-ended face massage brush</t>
+          <t>lymph brush for face and neck</t>
         </is>
       </c>
       <c r="U89" t="inlineStr"/>
@@ -6241,12 +6253,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -6273,7 +6285,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>nuventra facial brush</t>
+          <t>face brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U90" t="inlineStr"/>
@@ -6306,12 +6318,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -6338,7 +6350,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>face beauty workshop lymphatic brush</t>
+          <t>soft bristle face brush</t>
         </is>
       </c>
       <c r="U91" t="inlineStr"/>
@@ -6371,12 +6383,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -6398,12 +6410,12 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>koneva lymphatic face brush</t>
+          <t>lymphatic dry brush for face</t>
         </is>
       </c>
       <c r="U92" t="inlineStr"/>
@@ -6436,12 +6448,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -6463,12 +6475,12 @@
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>floriem lymphatic face brush</t>
+          <t>face sculpting brush lymphatic</t>
         </is>
       </c>
       <c r="U93" t="inlineStr"/>
@@ -6491,7 +6503,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6504,46 +6516,48 @@
           <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>avie_oct_rivales_ex</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_RIVALES_EX</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
       <c r="O94" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr"/>
+      <c r="P94" t="n">
+        <v>2</v>
+      </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>auvorra lymphatic contour face brush</t>
-        </is>
-      </c>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr"/>
+      <c r="W94" t="inlineStr"/>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
+        </is>
+      </c>
       <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="inlineStr"/>
       <c r="AA94" t="inlineStr"/>
@@ -6556,7 +6570,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6579,7 +6593,11 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>avie_oct_rivales_ex</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
@@ -6590,24 +6608,14 @@
       </c>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>kojeca lymphatic face brush</t>
-        </is>
-      </c>
+      <c r="R95" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
+      <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
@@ -6621,7 +6629,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6654,25 +6662,17 @@
         </is>
       </c>
       <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>avie 011</t>
+        </is>
+      </c>
       <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>nuevetra face brush</t>
-        </is>
-      </c>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
+      <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="inlineStr"/>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>kogeva lymphatic face brush</t>
+          <t>contour glow brush for face</t>
         </is>
       </c>
       <c r="U97" t="inlineStr"/>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>cecily braden lymphatic face brush</t>
+          <t>k glow face sculpting brush</t>
         </is>
       </c>
       <c r="U98" t="inlineStr"/>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>soothesilk facial contour brush</t>
+          <t>contour glow brush</t>
         </is>
       </c>
       <c r="U99" t="inlineStr"/>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>sefvako lymphatic contour face brush</t>
+          <t>lymphatic contour face brush k glow</t>
         </is>
       </c>
       <c r="U100" t="inlineStr"/>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>recuvia lymphatic contour face brush eliminate puffiness in minutes</t>
+          <t>contour glow face brush</t>
         </is>
       </c>
       <c r="U101" t="inlineStr"/>
@@ -7053,7 +7053,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>vough lymphatic contour face brush</t>
+          <t>contourglow brush</t>
         </is>
       </c>
       <c r="U102" t="inlineStr"/>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>akei lymphatic facial brush</t>
+          <t>skinn double-ended face massage brush</t>
         </is>
       </c>
       <c r="U103" t="inlineStr"/>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>aeli lymphatic face brush</t>
+          <t>nuventra facial brush</t>
         </is>
       </c>
       <c r="U104" t="inlineStr"/>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush puur house</t>
+          <t>face beauty workshop lymphatic brush</t>
         </is>
       </c>
       <c r="U105" t="inlineStr"/>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>koje a lymphatic face brush</t>
+          <t>koneva lymphatic face brush</t>
         </is>
       </c>
       <c r="U106" t="inlineStr"/>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>koheva lymphatic face brush</t>
+          <t>floriem lymphatic face brush</t>
         </is>
       </c>
       <c r="U107" t="inlineStr"/>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>awki lymphatic face brush</t>
+          <t>auvorra lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U108" t="inlineStr"/>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>kojovia face brush for lymphatic drainage</t>
+          <t>kojeca lymphatic face brush</t>
         </is>
       </c>
       <c r="U109" t="inlineStr"/>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>arki lymphatic face brush</t>
+          <t>nuevetra face brush</t>
         </is>
       </c>
       <c r="U110" t="inlineStr"/>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>puur house lymphatic contour face brush</t>
+          <t>kogeva lymphatic face brush</t>
         </is>
       </c>
       <c r="U111" t="inlineStr"/>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>lymphatic brush by cecily braden</t>
+          <t>cecily braden lymphatic face brush</t>
         </is>
       </c>
       <c r="U112" t="inlineStr"/>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>kojevs lymphatic face brush</t>
+          <t>soothesilk facial contour brush</t>
         </is>
       </c>
       <c r="U113" t="inlineStr"/>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>eteross lymphatic face brush</t>
+          <t>sefvako lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U114" t="inlineStr"/>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>vddo lymphatic contour face brush</t>
+          <t>recuvia lymphatic contour face brush eliminate puffiness in minutes</t>
         </is>
       </c>
       <c r="U115" t="inlineStr"/>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>vellorra lymphatic contour face brush</t>
+          <t>vough lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U116" t="inlineStr"/>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7996,51 +7996,49 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>AVIE_OCT_ASIN</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>AVIE_OCT_RIVALES_EX</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>avie_oct_rivales_ex</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>AVIE_OCT_ASIN</t>
-        </is>
-      </c>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
+      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P117" t="n">
-        <v>4</v>
-      </c>
+      <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr"/>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>akei lymphatic facial brush</t>
+        </is>
+      </c>
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr">
-        <is>
-          <t>Dynamic bids - down only</t>
-        </is>
-      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr"/>
       <c r="AA117" t="inlineStr"/>
@@ -8053,7 +8051,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8063,12 +8061,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AVIE_OCT_ASIN</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>avie_oct_asin</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -8076,11 +8074,7 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>avie_oct_asin</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
@@ -8091,14 +8085,24 @@
       </c>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
-      <c r="R118" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="S118" t="inlineStr"/>
-      <c r="T118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>aeli lymphatic face brush</t>
+        </is>
+      </c>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr"/>
       <c r="Z118" t="inlineStr"/>
@@ -8112,7 +8116,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8122,12 +8126,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>AVIE_OCT_ASIN</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>avie_oct_asin</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -8145,17 +8149,25 @@
         </is>
       </c>
       <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>avie 011</t>
-        </is>
-      </c>
+      <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
-      <c r="T119" t="inlineStr"/>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>lymphatic contour face brush puur house</t>
+        </is>
+      </c>
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X119" t="inlineStr"/>
       <c r="Y119" t="inlineStr"/>
       <c r="Z119" t="inlineStr"/>
@@ -8169,7 +8181,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Product Targeting</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8179,12 +8191,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>AVIE_OCT_ASIN</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>avie_oct_asin</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -8206,21 +8218,25 @@
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="T120" t="inlineStr"/>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>koje a lymphatic face brush</t>
+        </is>
+      </c>
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
-      <c r="W120" t="inlineStr"/>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr"/>
       <c r="Z120" t="inlineStr"/>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>asin="B0GFSMWTPK"</t>
-        </is>
-      </c>
+      <c r="AA120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8230,7 +8246,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Product Targeting</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8240,12 +8256,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>AVIE_OCT_ASIN</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>avie_oct_asin</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -8267,21 +8283,25 @@
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="T121" t="inlineStr"/>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>koheva lymphatic face brush</t>
+        </is>
+      </c>
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr"/>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr"/>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>asin="B0GVBQ7P79"</t>
-        </is>
-      </c>
+      <c r="AA121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8291,7 +8311,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Product Targeting</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8301,12 +8321,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>AVIE_OCT_ASIN</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>avie_oct_asin</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -8328,21 +8348,25 @@
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="T122" t="inlineStr"/>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>awki lymphatic face brush</t>
+        </is>
+      </c>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="inlineStr"/>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>asin="B0G3685P2S"</t>
-        </is>
-      </c>
+      <c r="AA122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8352,7 +8376,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8362,51 +8386,49 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>AVIE_OCT_DESCUBRIR_PH</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
+          <t>AVIE_OCT_RIVALES_EX</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>avie_oct_rivales_ex</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>AVIE_OCT_DESCUBRIR_PH</t>
-        </is>
-      </c>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
+      <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P123" t="n">
-        <v>3</v>
-      </c>
+      <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr"/>
-      <c r="T123" t="inlineStr"/>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>kojovia face brush for lymphatic drainage</t>
+        </is>
+      </c>
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr"/>
-      <c r="W123" t="inlineStr"/>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>Dynamic bids - down only</t>
-        </is>
-      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr"/>
       <c r="Y123" t="inlineStr"/>
       <c r="Z123" t="inlineStr"/>
       <c r="AA123" t="inlineStr"/>
@@ -8419,7 +8441,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8429,12 +8451,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>AVIE_OCT_DESCUBRIR_PH</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>avie_oct_descubrir_ph</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -8442,11 +8464,7 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>avie_oct_descubrir_ph</t>
-        </is>
-      </c>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
@@ -8457,14 +8475,24 @@
       </c>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
-      <c r="R124" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="S124" t="inlineStr"/>
-      <c r="T124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>arki lymphatic face brush</t>
+        </is>
+      </c>
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
-      <c r="W124" t="inlineStr"/>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X124" t="inlineStr"/>
       <c r="Y124" t="inlineStr"/>
       <c r="Z124" t="inlineStr"/>
@@ -8478,7 +8506,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8488,12 +8516,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>AVIE_OCT_DESCUBRIR_PH</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>avie_oct_descubrir_ph</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -8511,17 +8539,25 @@
         </is>
       </c>
       <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr">
-        <is>
-          <t>avie 011</t>
-        </is>
-      </c>
+      <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr"/>
-      <c r="T125" t="inlineStr"/>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>puur house lymphatic contour face brush</t>
+        </is>
+      </c>
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
-      <c r="W125" t="inlineStr"/>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X125" t="inlineStr"/>
       <c r="Y125" t="inlineStr"/>
       <c r="Z125" t="inlineStr"/>
@@ -8545,12 +8581,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>AVIE_OCT_DESCUBRIR_PH</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>avie_oct_descubrir_ph</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -8572,19 +8608,19 @@
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>lymphatic face brush</t>
+          <t>lymphatic brush by cecily braden</t>
         </is>
       </c>
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="X126" t="inlineStr"/>
@@ -8610,12 +8646,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>AVIE_OCT_DESCUBRIR_PH</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>avie_oct_descubrir_ph</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -8637,19 +8673,19 @@
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>lymphatic drainage brush</t>
+          <t>kojevs lymphatic face brush</t>
         </is>
       </c>
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr"/>
       <c r="W127" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="X127" t="inlineStr"/>
@@ -8675,12 +8711,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>AVIE_OCT_DESCUBRIR_PH</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>avie_oct_descubrir_ph</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -8702,19 +8738,19 @@
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>gua sha brush</t>
+          <t>eteross lymphatic face brush</t>
         </is>
       </c>
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
       <c r="W128" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="X128" t="inlineStr"/>
@@ -8740,12 +8776,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>AVIE_OCT_DESCUBRIR_PH</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>avie_oct_descubrir_ph</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -8767,19 +8803,19 @@
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>face sculpting brush</t>
+          <t>vddo lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr"/>
       <c r="W129" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="X129" t="inlineStr"/>
@@ -8805,12 +8841,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>AVIE_OCT_DESCUBRIR_PH</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>avie_oct_descubrir_ph</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -8832,19 +8868,19 @@
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>depuff brush</t>
+          <t>vellorra lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
       <c r="W130" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="X130" t="inlineStr"/>
@@ -8860,7 +8896,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8870,51 +8906,49 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>AVIE_OCT_RIVALES_EX</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>avie_oct_rivales_ex</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
-        </is>
-      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
+      <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P131" t="n">
-        <v>6</v>
-      </c>
+      <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
-      <c r="S131" t="inlineStr"/>
-      <c r="T131" t="inlineStr"/>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>nuvetra contour glow brush</t>
+        </is>
+      </c>
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr"/>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>Dynamic bids - down only</t>
-        </is>
-      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr"/>
       <c r="Z131" t="inlineStr"/>
       <c r="AA131" t="inlineStr"/>
@@ -8927,7 +8961,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8937,12 +8971,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -8950,11 +8984,7 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>avie_oct_auto_cosecha</t>
-        </is>
-      </c>
+      <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
@@ -8965,14 +8995,24 @@
       </c>
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
-      <c r="R132" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S132" t="inlineStr"/>
-      <c r="T132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>kojeva lymphatic brush face</t>
+        </is>
+      </c>
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
-      <c r="W132" t="inlineStr"/>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr"/>
       <c r="Z132" t="inlineStr"/>
@@ -8986,7 +9026,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8996,12 +9036,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -9019,17 +9059,25 @@
         </is>
       </c>
       <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr">
-        <is>
-          <t>avie 011</t>
-        </is>
-      </c>
+      <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
-      <c r="T133" t="inlineStr"/>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>akei lymphatic brush</t>
+        </is>
+      </c>
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr"/>
-      <c r="W133" t="inlineStr"/>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr"/>
       <c r="Z133" t="inlineStr"/>
@@ -9043,7 +9091,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Product Targeting</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9053,12 +9101,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -9080,21 +9128,25 @@
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="T134" t="inlineStr"/>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>koniva face brush</t>
+        </is>
+      </c>
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr"/>
-      <c r="W134" t="inlineStr"/>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr"/>
       <c r="Z134" t="inlineStr"/>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>close-match</t>
-        </is>
-      </c>
+      <c r="AA134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9104,7 +9156,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Product Targeting</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9114,12 +9166,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -9141,21 +9193,25 @@
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="T135" t="inlineStr"/>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>soothesilk facial brush</t>
+        </is>
+      </c>
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr"/>
-      <c r="W135" t="inlineStr"/>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="inlineStr"/>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>loose-match</t>
-        </is>
-      </c>
+      <c r="AA135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9165,7 +9221,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Product Targeting</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9175,48 +9231,54 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>avie_oct_auto_cosecha</t>
-        </is>
-      </c>
+          <t>AVIE_OCT_ASIN</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_ASIN</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
       <c r="O136" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P136" t="inlineStr"/>
+      <c r="P136" t="n">
+        <v>3</v>
+      </c>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
+      <c r="S136" t="inlineStr"/>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr"/>
       <c r="W136" t="inlineStr"/>
-      <c r="X136" t="inlineStr"/>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
+        </is>
+      </c>
       <c r="Y136" t="inlineStr"/>
       <c r="Z136" t="inlineStr"/>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>substitutes</t>
-        </is>
-      </c>
+      <c r="AA136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9226,7 +9288,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Product Targeting</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9236,12 +9298,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_ASIN</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_asin</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -9249,7 +9311,11 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>avie_oct_asin</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
@@ -9260,12 +9326,10 @@
       </c>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
-      <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
+      <c r="R137" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
@@ -9273,11 +9337,7 @@
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr"/>
       <c r="Z137" t="inlineStr"/>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>complements</t>
-        </is>
-      </c>
+      <c r="AA137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9287,7 +9347,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9297,12 +9357,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_ASIN</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_asin</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -9320,21 +9380,17 @@
         </is>
       </c>
       <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>avie 011</t>
+        </is>
+      </c>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr"/>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>dry brush for lymphatic drainage</t>
-        </is>
-      </c>
+      <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" t="inlineStr"/>
@@ -9348,7 +9404,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9358,12 +9414,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_ASIN</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_asin</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -9383,23 +9439,23 @@
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
-      <c r="S139" t="inlineStr"/>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>lymphatic drainage brush</t>
-        </is>
-      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="inlineStr"/>
-      <c r="AA139" t="inlineStr"/>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>asin="B0GFSMWTPK"</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9409,7 +9465,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9419,12 +9475,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_ASIN</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_asin</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -9444,23 +9500,23 @@
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
-      <c r="S140" t="inlineStr"/>
-      <c r="T140" t="inlineStr">
-        <is>
-          <t>lymphatic face brush</t>
-        </is>
-      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr"/>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="inlineStr"/>
-      <c r="AA140" t="inlineStr"/>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>asin="B0GVBQ7P79"</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9470,7 +9526,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9480,12 +9536,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_ASIN</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_asin</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -9505,23 +9561,23 @@
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr"/>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>face lymphatic drainage brush</t>
-        </is>
-      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr"/>
       <c r="Z141" t="inlineStr"/>
-      <c r="AA141" t="inlineStr"/>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>asin="B0G3685P2S"</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9531,7 +9587,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9541,45 +9597,51 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>avie_oct_auto_cosecha</t>
-        </is>
-      </c>
+          <t>AVIE_OCT_DESCUBRIR_PH</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_DESCUBRIR_PH</t>
+        </is>
+      </c>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
       <c r="O142" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P142" t="inlineStr"/>
+      <c r="P142" t="n">
+        <v>2</v>
+      </c>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr"/>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>lymphatic drainage brush for face</t>
-        </is>
-      </c>
+      <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr"/>
+      <c r="W142" t="inlineStr"/>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
+        </is>
+      </c>
       <c r="Y142" t="inlineStr"/>
       <c r="Z142" t="inlineStr"/>
       <c r="AA142" t="inlineStr"/>
@@ -9592,7 +9654,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9602,12 +9664,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_DESCUBRIR_PH</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_descubrir_ph</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -9615,7 +9677,11 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>avie_oct_descubrir_ph</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
@@ -9626,20 +9692,14 @@
       </c>
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
-      <c r="R143" t="inlineStr"/>
+      <c r="R143" t="n">
+        <v>0.55</v>
+      </c>
       <c r="S143" t="inlineStr"/>
-      <c r="T143" t="inlineStr">
-        <is>
-          <t>facial lymphatic drainage brush</t>
-        </is>
-      </c>
+      <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr"/>
       <c r="Z143" t="inlineStr"/>
@@ -9653,7 +9713,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9663,12 +9723,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_DESCUBRIR_PH</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_descubrir_ph</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -9686,21 +9746,17 @@
         </is>
       </c>
       <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>avie 011</t>
+        </is>
+      </c>
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr"/>
-      <c r="T144" t="inlineStr">
-        <is>
-          <t>facial brush for lymphatic drainage</t>
-        </is>
-      </c>
+      <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" t="inlineStr"/>
@@ -9714,7 +9770,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9724,12 +9780,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_DESCUBRIR_PH</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_descubrir_ph</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -9749,17 +9805,21 @@
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
-      <c r="S145" t="inlineStr"/>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>guasha brush for face</t>
+          <t>lymphatic face brush</t>
         </is>
       </c>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
       <c r="W145" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
@@ -9775,7 +9835,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9785,12 +9845,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_DESCUBRIR_PH</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_descubrir_ph</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -9810,17 +9870,21 @@
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
-      <c r="S146" t="inlineStr"/>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>guasha brush</t>
+          <t>lymphatic drainage brush</t>
         </is>
       </c>
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr"/>
       <c r="W146" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
@@ -9836,7 +9900,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9846,12 +9910,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_DESCUBRIR_PH</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_descubrir_ph</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -9871,7 +9935,11 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr"/>
-      <c r="S147" t="inlineStr"/>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
       <c r="T147" t="inlineStr">
         <is>
           <t>gua sha brush</t>
@@ -9881,7 +9949,7 @@
       <c r="V147" t="inlineStr"/>
       <c r="W147" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
@@ -9897,7 +9965,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9907,12 +9975,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_DESCUBRIR_PH</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_descubrir_ph</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -9932,17 +10000,21 @@
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr"/>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>gua sha brush for face</t>
+          <t>face sculpting brush</t>
         </is>
       </c>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr"/>
       <c r="W148" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
@@ -9958,7 +10030,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9968,12 +10040,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_DESCUBRIR_PH</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_descubrir_ph</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -9993,17 +10065,21 @@
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr"/>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>lymphatic drainage brushes</t>
+          <t>depuff brush</t>
         </is>
       </c>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr"/>
       <c r="W149" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>phrase</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
@@ -10019,7 +10095,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -10032,42 +10108,48 @@
           <t>AVIE_OCT_AUTO_COSECHA</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>avie_oct_auto_cosecha</t>
-        </is>
-      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P150" t="inlineStr"/>
+      <c r="P150" t="n">
+        <v>3</v>
+      </c>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr"/>
-      <c r="T150" t="inlineStr">
-        <is>
-          <t>facial lymphatic brush</t>
-        </is>
-      </c>
+      <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr"/>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr"/>
+      <c r="W150" t="inlineStr"/>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
+        </is>
+      </c>
       <c r="Y150" t="inlineStr"/>
       <c r="Z150" t="inlineStr"/>
       <c r="AA150" t="inlineStr"/>
@@ -10080,7 +10162,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10103,7 +10185,11 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
@@ -10114,20 +10200,14 @@
       </c>
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
-      <c r="R151" t="inlineStr"/>
+      <c r="R151" t="n">
+        <v>0.4</v>
+      </c>
       <c r="S151" t="inlineStr"/>
-      <c r="T151" t="inlineStr">
-        <is>
-          <t>dry face brush for lymphatic drainage</t>
-        </is>
-      </c>
+      <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr"/>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W151" t="inlineStr"/>
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr"/>
       <c r="Z151" t="inlineStr"/>
@@ -10141,7 +10221,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -10174,21 +10254,17 @@
         </is>
       </c>
       <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>avie 011</t>
+        </is>
+      </c>
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr"/>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>pink lymphatic drainage brush</t>
-        </is>
-      </c>
+      <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W152" t="inlineStr"/>
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="inlineStr"/>
@@ -10202,7 +10278,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10237,23 +10313,23 @@
       <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr"/>
-      <c r="S153" t="inlineStr"/>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>pink lymphatic contour face brush</t>
-        </is>
-      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr"/>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W153" t="inlineStr"/>
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr"/>
       <c r="Z153" t="inlineStr"/>
-      <c r="AA153" t="inlineStr"/>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>loose-match</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10263,7 +10339,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -10292,29 +10368,27 @@
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>paused</t>
         </is>
       </c>
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr"/>
-      <c r="T154" t="inlineStr">
-        <is>
-          <t>pink lymphatic face brush</t>
-        </is>
-      </c>
+      <c r="S154" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W154" t="inlineStr"/>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr"/>
       <c r="Z154" t="inlineStr"/>
-      <c r="AA154" t="inlineStr"/>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>close-match</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10324,7 +10398,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10353,29 +10427,27 @@
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>paused</t>
         </is>
       </c>
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
-      <c r="S155" t="inlineStr"/>
-      <c r="T155" t="inlineStr">
-        <is>
-          <t>skin brush for face</t>
-        </is>
-      </c>
+      <c r="S155" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr"/>
-      <c r="W155" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W155" t="inlineStr"/>
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr"/>
       <c r="Z155" t="inlineStr"/>
-      <c r="AA155" t="inlineStr"/>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>substitutes</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10385,7 +10457,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10414,29 +10486,27 @@
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>paused</t>
         </is>
       </c>
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr"/>
-      <c r="T156" t="inlineStr">
-        <is>
-          <t>soft guasha facial brush</t>
-        </is>
-      </c>
+      <c r="S156" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr"/>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W156" t="inlineStr"/>
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr"/>
       <c r="Z156" t="inlineStr"/>
-      <c r="AA156" t="inlineStr"/>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>complements</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10484,7 +10554,7 @@
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr">
         <is>
-          <t>depuffing brush for face</t>
+          <t>dry brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U157" t="inlineStr"/>
@@ -10545,7 +10615,7 @@
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr">
         <is>
-          <t>brush for face drainage</t>
+          <t>lymphatic drainage brush</t>
         </is>
       </c>
       <c r="U158" t="inlineStr"/>
@@ -10606,7 +10676,7 @@
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush soft bristles</t>
+          <t>lymphatic face brush</t>
         </is>
       </c>
       <c r="U159" t="inlineStr"/>
@@ -10667,7 +10737,7 @@
       <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr">
         <is>
-          <t>lymphatic drainage brush soft</t>
+          <t>face lymphatic drainage brush</t>
         </is>
       </c>
       <c r="U160" t="inlineStr"/>
@@ -10728,7 +10798,7 @@
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr">
         <is>
-          <t>face drainage brush</t>
+          <t>lymphatic drainage brush for face</t>
         </is>
       </c>
       <c r="U161" t="inlineStr"/>
@@ -10789,7 +10859,7 @@
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr">
         <is>
-          <t>de-bloat face sculpting brush</t>
+          <t>facial lymphatic drainage brush</t>
         </is>
       </c>
       <c r="U162" t="inlineStr"/>
@@ -10850,7 +10920,7 @@
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr">
         <is>
-          <t>gua sha dry brush</t>
+          <t>facial brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U163" t="inlineStr"/>
@@ -10911,7 +10981,7 @@
       <c r="S164" t="inlineStr"/>
       <c r="T164" t="inlineStr">
         <is>
-          <t>face brush gua sha</t>
+          <t>guasha brush for face</t>
         </is>
       </c>
       <c r="U164" t="inlineStr"/>
@@ -10972,7 +11042,7 @@
       <c r="S165" t="inlineStr"/>
       <c r="T165" t="inlineStr">
         <is>
-          <t>gua sha face brush</t>
+          <t>guasha brush</t>
         </is>
       </c>
       <c r="U165" t="inlineStr"/>
@@ -11033,7 +11103,7 @@
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush korean</t>
+          <t>gua sha brush</t>
         </is>
       </c>
       <c r="U166" t="inlineStr"/>
@@ -11094,7 +11164,7 @@
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr">
         <is>
-          <t>guasha face brush</t>
+          <t>gua sha brush for face</t>
         </is>
       </c>
       <c r="U167" t="inlineStr"/>
@@ -11155,7 +11225,7 @@
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr">
         <is>
-          <t>face brushes for lymphatic drainage</t>
+          <t>lymphatic drainage brushes</t>
         </is>
       </c>
       <c r="U168" t="inlineStr"/>
@@ -11216,7 +11286,7 @@
       <c r="S169" t="inlineStr"/>
       <c r="T169" t="inlineStr">
         <is>
-          <t>brush guasha for face</t>
+          <t>facial lymphatic brush</t>
         </is>
       </c>
       <c r="U169" t="inlineStr"/>
@@ -11277,7 +11347,7 @@
       <c r="S170" t="inlineStr"/>
       <c r="T170" t="inlineStr">
         <is>
-          <t>lymphatic drainage brush face</t>
+          <t>dry face brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U170" t="inlineStr"/>
@@ -11338,7 +11408,7 @@
       <c r="S171" t="inlineStr"/>
       <c r="T171" t="inlineStr">
         <is>
-          <t>gua sha facial brush</t>
+          <t>pink lymphatic drainage brush</t>
         </is>
       </c>
       <c r="U171" t="inlineStr"/>
@@ -11399,7 +11469,7 @@
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr">
         <is>
-          <t>lymphatic facial drainage brush</t>
+          <t>pink lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U172" t="inlineStr"/>
@@ -11460,7 +11530,7 @@
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr">
         <is>
-          <t>face gua sha brush</t>
+          <t>pink lymphatic face brush</t>
         </is>
       </c>
       <c r="U173" t="inlineStr"/>
@@ -11521,7 +11591,7 @@
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr">
         <is>
-          <t>contour facial brush</t>
+          <t>skin brush for face</t>
         </is>
       </c>
       <c r="U174" t="inlineStr"/>
@@ -11582,7 +11652,7 @@
       <c r="S175" t="inlineStr"/>
       <c r="T175" t="inlineStr">
         <is>
-          <t>contour brush lymphatic drainage</t>
+          <t>soft guasha facial brush</t>
         </is>
       </c>
       <c r="U175" t="inlineStr"/>
@@ -11643,7 +11713,7 @@
       <c r="S176" t="inlineStr"/>
       <c r="T176" t="inlineStr">
         <is>
-          <t>facial contour brush lymphatic</t>
+          <t>depuffing brush for face</t>
         </is>
       </c>
       <c r="U176" t="inlineStr"/>
@@ -11704,7 +11774,7 @@
       <c r="S177" t="inlineStr"/>
       <c r="T177" t="inlineStr">
         <is>
-          <t>lymphatic beauty brush</t>
+          <t>brush for face drainage</t>
         </is>
       </c>
       <c r="U177" t="inlineStr"/>
@@ -11765,7 +11835,7 @@
       <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr">
         <is>
-          <t>gua sha dry brush for face</t>
+          <t>lymphatic contour face brush soft bristles</t>
         </is>
       </c>
       <c r="U178" t="inlineStr"/>
@@ -11826,7 +11896,7 @@
       <c r="S179" t="inlineStr"/>
       <c r="T179" t="inlineStr">
         <is>
-          <t>facial sculpting brushes for lymphatic drainage</t>
+          <t>lymphatic drainage brush soft</t>
         </is>
       </c>
       <c r="U179" t="inlineStr"/>
@@ -11887,7 +11957,7 @@
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr">
         <is>
-          <t>lymphatic drainage facial brush</t>
+          <t>face drainage brush</t>
         </is>
       </c>
       <c r="U180" t="inlineStr"/>
@@ -11948,7 +12018,7 @@
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush soft</t>
+          <t>de-bloat face sculpting brush</t>
         </is>
       </c>
       <c r="U181" t="inlineStr"/>
@@ -12009,7 +12079,7 @@
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr">
         <is>
-          <t>lymphatic drain face brush</t>
+          <t>gua sha dry brush</t>
         </is>
       </c>
       <c r="U182" t="inlineStr"/>
@@ -12070,7 +12140,7 @@
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr">
         <is>
-          <t>facial sculpting brush</t>
+          <t>face brush gua sha</t>
         </is>
       </c>
       <c r="U183" t="inlineStr"/>
@@ -12131,7 +12201,7 @@
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr">
         <is>
-          <t>soft face brush lymphatic</t>
+          <t>gua sha face brush</t>
         </is>
       </c>
       <c r="U184" t="inlineStr"/>
@@ -12192,7 +12262,7 @@
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr">
         <is>
-          <t>lymphatic drain brush for face</t>
+          <t>lymphatic contour face brush korean</t>
         </is>
       </c>
       <c r="U185" t="inlineStr"/>
@@ -12253,7 +12323,7 @@
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr">
         <is>
-          <t>facial brushes for lymphatic drainage</t>
+          <t>guasha face brush</t>
         </is>
       </c>
       <c r="U186" t="inlineStr"/>
@@ -12314,7 +12384,7 @@
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr">
         <is>
-          <t>lymphatic draining brush for face</t>
+          <t>face brushes for lymphatic drainage</t>
         </is>
       </c>
       <c r="U187" t="inlineStr"/>
@@ -12375,7 +12445,7 @@
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr">
         <is>
-          <t>facial drainage brush</t>
+          <t>brush guasha for face</t>
         </is>
       </c>
       <c r="U188" t="inlineStr"/>
@@ -12436,7 +12506,7 @@
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr">
         <is>
-          <t>sculpt brush for face</t>
+          <t>lymphatic drainage brush face</t>
         </is>
       </c>
       <c r="U189" t="inlineStr"/>
@@ -12497,7 +12567,7 @@
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr">
         <is>
-          <t>korean face lifting brush</t>
+          <t>gua sha facial brush</t>
         </is>
       </c>
       <c r="U190" t="inlineStr"/>
@@ -12558,7 +12628,7 @@
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr">
         <is>
-          <t>facial lymph drainage brush</t>
+          <t>lymphatic facial drainage brush</t>
         </is>
       </c>
       <c r="U191" t="inlineStr"/>
@@ -12619,7 +12689,7 @@
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr">
         <is>
-          <t>lymphatic facial contour brush</t>
+          <t>face gua sha brush</t>
         </is>
       </c>
       <c r="U192" t="inlineStr"/>
@@ -12680,7 +12750,7 @@
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr">
         <is>
-          <t>sculpting face brush</t>
+          <t>contour facial brush</t>
         </is>
       </c>
       <c r="U193" t="inlineStr"/>
@@ -12741,7 +12811,7 @@
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr">
         <is>
-          <t>dry lymphatic massage brush for face</t>
+          <t>contour brush lymphatic drainage</t>
         </is>
       </c>
       <c r="U194" t="inlineStr"/>
@@ -12802,7 +12872,7 @@
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr">
         <is>
-          <t>lymphatic contour brush for face</t>
+          <t>facial contour brush lymphatic</t>
         </is>
       </c>
       <c r="U195" t="inlineStr"/>
@@ -12863,7 +12933,7 @@
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr">
         <is>
-          <t>face brush lymphatic drainage</t>
+          <t>lymphatic beauty brush</t>
         </is>
       </c>
       <c r="U196" t="inlineStr"/>
@@ -12924,7 +12994,7 @@
       <c r="S197" t="inlineStr"/>
       <c r="T197" t="inlineStr">
         <is>
-          <t>facial contour brush</t>
+          <t>gua sha dry brush for face</t>
         </is>
       </c>
       <c r="U197" t="inlineStr"/>
@@ -12985,7 +13055,7 @@
       <c r="S198" t="inlineStr"/>
       <c r="T198" t="inlineStr">
         <is>
-          <t>contour lymphatic face brush</t>
+          <t>facial sculpting brushes for lymphatic drainage</t>
         </is>
       </c>
       <c r="U198" t="inlineStr"/>
@@ -13046,7 +13116,7 @@
       <c r="S199" t="inlineStr"/>
       <c r="T199" t="inlineStr">
         <is>
-          <t>dry brush face</t>
+          <t>lymphatic drainage facial brush</t>
         </is>
       </c>
       <c r="U199" t="inlineStr"/>
@@ -13107,7 +13177,7 @@
       <c r="S200" t="inlineStr"/>
       <c r="T200" t="inlineStr">
         <is>
-          <t>face lymphatic brush</t>
+          <t>lymphatic contour face brush soft</t>
         </is>
       </c>
       <c r="U200" t="inlineStr"/>
@@ -13168,7 +13238,7 @@
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr">
         <is>
-          <t>korean brush for face</t>
+          <t>lymphatic drain face brush</t>
         </is>
       </c>
       <c r="U201" t="inlineStr"/>
@@ -13229,7 +13299,7 @@
       <c r="S202" t="inlineStr"/>
       <c r="T202" t="inlineStr">
         <is>
-          <t>face lymphatic contour brush</t>
+          <t>facial sculpting brush</t>
         </is>
       </c>
       <c r="U202" t="inlineStr"/>
@@ -13290,7 +13360,7 @@
       <c r="S203" t="inlineStr"/>
       <c r="T203" t="inlineStr">
         <is>
-          <t>face massage brush</t>
+          <t>soft face brush lymphatic</t>
         </is>
       </c>
       <c r="U203" t="inlineStr"/>
@@ -13351,7 +13421,7 @@
       <c r="S204" t="inlineStr"/>
       <c r="T204" t="inlineStr">
         <is>
-          <t>dry brush for lymphatic drainage face</t>
+          <t>lymphatic drain brush for face</t>
         </is>
       </c>
       <c r="U204" t="inlineStr"/>
@@ -13412,7 +13482,7 @@
       <c r="S205" t="inlineStr"/>
       <c r="T205" t="inlineStr">
         <is>
-          <t>face lifting brush</t>
+          <t>facial brushes for lymphatic drainage</t>
         </is>
       </c>
       <c r="U205" t="inlineStr"/>
@@ -13473,7 +13543,7 @@
       <c r="S206" t="inlineStr"/>
       <c r="T206" t="inlineStr">
         <is>
-          <t>depuff brush for face</t>
+          <t>lymphatic draining brush for face</t>
         </is>
       </c>
       <c r="U206" t="inlineStr"/>
@@ -13534,7 +13604,7 @@
       <c r="S207" t="inlineStr"/>
       <c r="T207" t="inlineStr">
         <is>
-          <t>face dry brush for lymphatic drainage</t>
+          <t>facial drainage brush</t>
         </is>
       </c>
       <c r="U207" t="inlineStr"/>
@@ -13595,7 +13665,7 @@
       <c r="S208" t="inlineStr"/>
       <c r="T208" t="inlineStr">
         <is>
-          <t>korean lymphatic face brush</t>
+          <t>sculpt brush for face</t>
         </is>
       </c>
       <c r="U208" t="inlineStr"/>
@@ -13656,7 +13726,7 @@
       <c r="S209" t="inlineStr"/>
       <c r="T209" t="inlineStr">
         <is>
-          <t>contour glow brush for face</t>
+          <t>korean face lifting brush</t>
         </is>
       </c>
       <c r="U209" t="inlineStr"/>
@@ -13717,7 +13787,7 @@
       <c r="S210" t="inlineStr"/>
       <c r="T210" t="inlineStr">
         <is>
-          <t>k glow face sculpting brush</t>
+          <t>facial lymph drainage brush</t>
         </is>
       </c>
       <c r="U210" t="inlineStr"/>
@@ -13778,7 +13848,7 @@
       <c r="S211" t="inlineStr"/>
       <c r="T211" t="inlineStr">
         <is>
-          <t>contour glow brush</t>
+          <t>lymphatic facial contour brush</t>
         </is>
       </c>
       <c r="U211" t="inlineStr"/>
@@ -13839,7 +13909,7 @@
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush k glow</t>
+          <t>sculpting face brush</t>
         </is>
       </c>
       <c r="U212" t="inlineStr"/>
@@ -13900,7 +13970,7 @@
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr">
         <is>
-          <t>contour glow face brush</t>
+          <t>dry lymphatic massage brush for face</t>
         </is>
       </c>
       <c r="U213" t="inlineStr"/>
@@ -13961,7 +14031,7 @@
       <c r="S214" t="inlineStr"/>
       <c r="T214" t="inlineStr">
         <is>
-          <t>contourglow brush</t>
+          <t>lymphatic contour brush for face</t>
         </is>
       </c>
       <c r="U214" t="inlineStr"/>
@@ -14022,7 +14092,7 @@
       <c r="S215" t="inlineStr"/>
       <c r="T215" t="inlineStr">
         <is>
-          <t>skinn double-ended face massage brush</t>
+          <t>face brush lymphatic drainage</t>
         </is>
       </c>
       <c r="U215" t="inlineStr"/>
@@ -14083,7 +14153,7 @@
       <c r="S216" t="inlineStr"/>
       <c r="T216" t="inlineStr">
         <is>
-          <t>nuventra facial brush</t>
+          <t>facial contour brush</t>
         </is>
       </c>
       <c r="U216" t="inlineStr"/>
@@ -14144,7 +14214,7 @@
       <c r="S217" t="inlineStr"/>
       <c r="T217" t="inlineStr">
         <is>
-          <t>face beauty workshop lymphatic brush</t>
+          <t>contour lymphatic face brush</t>
         </is>
       </c>
       <c r="U217" t="inlineStr"/>
@@ -14205,7 +14275,7 @@
       <c r="S218" t="inlineStr"/>
       <c r="T218" t="inlineStr">
         <is>
-          <t>koneva lymphatic face brush</t>
+          <t>dry brush face</t>
         </is>
       </c>
       <c r="U218" t="inlineStr"/>
@@ -14266,7 +14336,7 @@
       <c r="S219" t="inlineStr"/>
       <c r="T219" t="inlineStr">
         <is>
-          <t>floriem lymphatic face brush</t>
+          <t>face lymphatic brush</t>
         </is>
       </c>
       <c r="U219" t="inlineStr"/>
@@ -14327,7 +14397,7 @@
       <c r="S220" t="inlineStr"/>
       <c r="T220" t="inlineStr">
         <is>
-          <t>auvorra lymphatic contour face brush</t>
+          <t>korean brush for face</t>
         </is>
       </c>
       <c r="U220" t="inlineStr"/>
@@ -14388,7 +14458,7 @@
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr">
         <is>
-          <t>kojeca lymphatic face brush</t>
+          <t>face lymphatic contour brush</t>
         </is>
       </c>
       <c r="U221" t="inlineStr"/>
@@ -14449,7 +14519,7 @@
       <c r="S222" t="inlineStr"/>
       <c r="T222" t="inlineStr">
         <is>
-          <t>nuevetra face brush</t>
+          <t>face massage brush</t>
         </is>
       </c>
       <c r="U222" t="inlineStr"/>
@@ -14510,7 +14580,7 @@
       <c r="S223" t="inlineStr"/>
       <c r="T223" t="inlineStr">
         <is>
-          <t>kogeva lymphatic face brush</t>
+          <t>dry brush for lymphatic drainage face</t>
         </is>
       </c>
       <c r="U223" t="inlineStr"/>
@@ -14571,7 +14641,7 @@
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr">
         <is>
-          <t>cecily braden lymphatic face brush</t>
+          <t>face lifting brush</t>
         </is>
       </c>
       <c r="U224" t="inlineStr"/>
@@ -14632,7 +14702,7 @@
       <c r="S225" t="inlineStr"/>
       <c r="T225" t="inlineStr">
         <is>
-          <t>soothesilk facial contour brush</t>
+          <t>depuff brush for face</t>
         </is>
       </c>
       <c r="U225" t="inlineStr"/>
@@ -14693,7 +14763,7 @@
       <c r="S226" t="inlineStr"/>
       <c r="T226" t="inlineStr">
         <is>
-          <t>sefvako lymphatic contour face brush</t>
+          <t>face dry brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U226" t="inlineStr"/>
@@ -14754,7 +14824,7 @@
       <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr">
         <is>
-          <t>recuvia lymphatic contour face brush eliminate puffiness in minutes</t>
+          <t>korean lymphatic face brush</t>
         </is>
       </c>
       <c r="U227" t="inlineStr"/>
@@ -14815,7 +14885,7 @@
       <c r="S228" t="inlineStr"/>
       <c r="T228" t="inlineStr">
         <is>
-          <t>vough lymphatic contour face brush</t>
+          <t>contour glow brush for face</t>
         </is>
       </c>
       <c r="U228" t="inlineStr"/>
@@ -14876,7 +14946,7 @@
       <c r="S229" t="inlineStr"/>
       <c r="T229" t="inlineStr">
         <is>
-          <t>akei lymphatic facial brush</t>
+          <t>k glow face sculpting brush</t>
         </is>
       </c>
       <c r="U229" t="inlineStr"/>
@@ -14937,7 +15007,7 @@
       <c r="S230" t="inlineStr"/>
       <c r="T230" t="inlineStr">
         <is>
-          <t>aeli lymphatic face brush</t>
+          <t>contour glow brush</t>
         </is>
       </c>
       <c r="U230" t="inlineStr"/>
@@ -14998,7 +15068,7 @@
       <c r="S231" t="inlineStr"/>
       <c r="T231" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush puur house</t>
+          <t>lymphatic contour face brush k glow</t>
         </is>
       </c>
       <c r="U231" t="inlineStr"/>
@@ -15059,7 +15129,7 @@
       <c r="S232" t="inlineStr"/>
       <c r="T232" t="inlineStr">
         <is>
-          <t>koje a lymphatic face brush</t>
+          <t>contour glow face brush</t>
         </is>
       </c>
       <c r="U232" t="inlineStr"/>
@@ -15120,7 +15190,7 @@
       <c r="S233" t="inlineStr"/>
       <c r="T233" t="inlineStr">
         <is>
-          <t>koheva lymphatic face brush</t>
+          <t>contourglow brush</t>
         </is>
       </c>
       <c r="U233" t="inlineStr"/>
@@ -15181,7 +15251,7 @@
       <c r="S234" t="inlineStr"/>
       <c r="T234" t="inlineStr">
         <is>
-          <t>awki lymphatic face brush</t>
+          <t>skinn double-ended face massage brush</t>
         </is>
       </c>
       <c r="U234" t="inlineStr"/>
@@ -15242,7 +15312,7 @@
       <c r="S235" t="inlineStr"/>
       <c r="T235" t="inlineStr">
         <is>
-          <t>kojovia face brush for lymphatic drainage</t>
+          <t>nuventra facial brush</t>
         </is>
       </c>
       <c r="U235" t="inlineStr"/>
@@ -15303,7 +15373,7 @@
       <c r="S236" t="inlineStr"/>
       <c r="T236" t="inlineStr">
         <is>
-          <t>arki lymphatic face brush</t>
+          <t>face beauty workshop lymphatic brush</t>
         </is>
       </c>
       <c r="U236" t="inlineStr"/>
@@ -15364,7 +15434,7 @@
       <c r="S237" t="inlineStr"/>
       <c r="T237" t="inlineStr">
         <is>
-          <t>puur house lymphatic contour face brush</t>
+          <t>koneva lymphatic face brush</t>
         </is>
       </c>
       <c r="U237" t="inlineStr"/>
@@ -15425,7 +15495,7 @@
       <c r="S238" t="inlineStr"/>
       <c r="T238" t="inlineStr">
         <is>
-          <t>lymphatic brush by cecily braden</t>
+          <t>floriem lymphatic face brush</t>
         </is>
       </c>
       <c r="U238" t="inlineStr"/>
@@ -15486,7 +15556,7 @@
       <c r="S239" t="inlineStr"/>
       <c r="T239" t="inlineStr">
         <is>
-          <t>kojevs lymphatic face brush</t>
+          <t>auvorra lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U239" t="inlineStr"/>
@@ -15547,7 +15617,7 @@
       <c r="S240" t="inlineStr"/>
       <c r="T240" t="inlineStr">
         <is>
-          <t>eteross lymphatic face brush</t>
+          <t>kojeca lymphatic face brush</t>
         </is>
       </c>
       <c r="U240" t="inlineStr"/>
@@ -15608,7 +15678,7 @@
       <c r="S241" t="inlineStr"/>
       <c r="T241" t="inlineStr">
         <is>
-          <t>vddo lymphatic contour face brush</t>
+          <t>nuevetra face brush</t>
         </is>
       </c>
       <c r="U241" t="inlineStr"/>
@@ -15669,7 +15739,7 @@
       <c r="S242" t="inlineStr"/>
       <c r="T242" t="inlineStr">
         <is>
-          <t>vellorra lymphatic contour face brush</t>
+          <t>kogeva lymphatic face brush</t>
         </is>
       </c>
       <c r="U242" t="inlineStr"/>
@@ -15730,7 +15800,7 @@
       <c r="S243" t="inlineStr"/>
       <c r="T243" t="inlineStr">
         <is>
-          <t>gua sha facial tools</t>
+          <t>cecily braden lymphatic face brush</t>
         </is>
       </c>
       <c r="U243" t="inlineStr"/>
@@ -15791,7 +15861,7 @@
       <c r="S244" t="inlineStr"/>
       <c r="T244" t="inlineStr">
         <is>
-          <t>kojeva lymphatic face brush</t>
+          <t>soothesilk facial contour brush</t>
         </is>
       </c>
       <c r="U244" t="inlineStr"/>
@@ -15852,7 +15922,7 @@
       <c r="S245" t="inlineStr"/>
       <c r="T245" t="inlineStr">
         <is>
-          <t>kitsch lymphatic contour face brush</t>
+          <t>sefvako lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U245" t="inlineStr"/>
@@ -15913,7 +15983,7 @@
       <c r="S246" t="inlineStr"/>
       <c r="T246" t="inlineStr">
         <is>
-          <t>facial brush</t>
+          <t>recuvia lymphatic contour face brush eliminate puffiness in minutes</t>
         </is>
       </c>
       <c r="U246" t="inlineStr"/>
@@ -15974,7 +16044,7 @@
       <c r="S247" t="inlineStr"/>
       <c r="T247" t="inlineStr">
         <is>
-          <t>guasha tool for face</t>
+          <t>vough lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U247" t="inlineStr"/>
@@ -16035,14 +16105,14 @@
       <c r="S248" t="inlineStr"/>
       <c r="T248" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>akei lymphatic facial brush</t>
         </is>
       </c>
       <c r="U248" t="inlineStr"/>
       <c r="V248" t="inlineStr"/>
       <c r="W248" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
       <c r="X248" t="inlineStr"/>
@@ -16096,14 +16166,14 @@
       <c r="S249" t="inlineStr"/>
       <c r="T249" t="inlineStr">
         <is>
-          <t>makeup</t>
+          <t>aeli lymphatic face brush</t>
         </is>
       </c>
       <c r="U249" t="inlineStr"/>
       <c r="V249" t="inlineStr"/>
       <c r="W249" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
       <c r="X249" t="inlineStr"/>
@@ -16157,14 +16227,14 @@
       <c r="S250" t="inlineStr"/>
       <c r="T250" t="inlineStr">
         <is>
-          <t>body</t>
+          <t>lymphatic contour face brush puur house</t>
         </is>
       </c>
       <c r="U250" t="inlineStr"/>
       <c r="V250" t="inlineStr"/>
       <c r="W250" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
       <c r="X250" t="inlineStr"/>
@@ -16218,14 +16288,14 @@
       <c r="S251" t="inlineStr"/>
       <c r="T251" t="inlineStr">
         <is>
-          <t>drops</t>
+          <t>koje a lymphatic face brush</t>
         </is>
       </c>
       <c r="U251" t="inlineStr"/>
       <c r="V251" t="inlineStr"/>
       <c r="W251" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
       <c r="X251" t="inlineStr"/>
@@ -16279,14 +16349,14 @@
       <c r="S252" t="inlineStr"/>
       <c r="T252" t="inlineStr">
         <is>
-          <t>supplement</t>
+          <t>koheva lymphatic face brush</t>
         </is>
       </c>
       <c r="U252" t="inlineStr"/>
       <c r="V252" t="inlineStr"/>
       <c r="W252" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
       <c r="X252" t="inlineStr"/>
@@ -16340,14 +16410,14 @@
       <c r="S253" t="inlineStr"/>
       <c r="T253" t="inlineStr">
         <is>
-          <t>pills</t>
+          <t>awki lymphatic face brush</t>
         </is>
       </c>
       <c r="U253" t="inlineStr"/>
       <c r="V253" t="inlineStr"/>
       <c r="W253" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
       <c r="X253" t="inlineStr"/>
@@ -16401,14 +16471,14 @@
       <c r="S254" t="inlineStr"/>
       <c r="T254" t="inlineStr">
         <is>
-          <t>toothbrush</t>
+          <t>kojovia face brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U254" t="inlineStr"/>
       <c r="V254" t="inlineStr"/>
       <c r="W254" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
       <c r="X254" t="inlineStr"/>
@@ -16462,14 +16532,14 @@
       <c r="S255" t="inlineStr"/>
       <c r="T255" t="inlineStr">
         <is>
-          <t>cleansing</t>
+          <t>arki lymphatic face brush</t>
         </is>
       </c>
       <c r="U255" t="inlineStr"/>
       <c r="V255" t="inlineStr"/>
       <c r="W255" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
       <c r="X255" t="inlineStr"/>
@@ -16523,14 +16593,14 @@
       <c r="S256" t="inlineStr"/>
       <c r="T256" t="inlineStr">
         <is>
-          <t>exfoliating</t>
+          <t>puur house lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U256" t="inlineStr"/>
       <c r="V256" t="inlineStr"/>
       <c r="W256" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
       <c r="X256" t="inlineStr"/>
@@ -16584,14 +16654,14 @@
       <c r="S257" t="inlineStr"/>
       <c r="T257" t="inlineStr">
         <is>
-          <t>powder</t>
+          <t>lymphatic brush by cecily braden</t>
         </is>
       </c>
       <c r="U257" t="inlineStr"/>
       <c r="V257" t="inlineStr"/>
       <c r="W257" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
       <c r="X257" t="inlineStr"/>
@@ -16645,14 +16715,14 @@
       <c r="S258" t="inlineStr"/>
       <c r="T258" t="inlineStr">
         <is>
-          <t>ice roller</t>
+          <t>kojevs lymphatic face brush</t>
         </is>
       </c>
       <c r="U258" t="inlineStr"/>
       <c r="V258" t="inlineStr"/>
       <c r="W258" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
       <c r="X258" t="inlineStr"/>
@@ -16668,7 +16738,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Negative Product Targeting</t>
+          <t>Negative Keyword</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16704,18 +16774,22 @@
       <c r="Q259" t="inlineStr"/>
       <c r="R259" t="inlineStr"/>
       <c r="S259" t="inlineStr"/>
-      <c r="T259" t="inlineStr"/>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>eteross lymphatic face brush</t>
+        </is>
+      </c>
       <c r="U259" t="inlineStr"/>
       <c r="V259" t="inlineStr"/>
-      <c r="W259" t="inlineStr"/>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
       <c r="X259" t="inlineStr"/>
       <c r="Y259" t="inlineStr"/>
       <c r="Z259" t="inlineStr"/>
-      <c r="AA259" t="inlineStr">
-        <is>
-          <t>asin="B0FD354L27"</t>
-        </is>
-      </c>
+      <c r="AA259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -16725,7 +16799,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Negative Product Targeting</t>
+          <t>Negative Keyword</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16761,14 +16835,2572 @@
       <c r="Q260" t="inlineStr"/>
       <c r="R260" t="inlineStr"/>
       <c r="S260" t="inlineStr"/>
-      <c r="T260" t="inlineStr"/>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>vddo lymphatic contour face brush</t>
+        </is>
+      </c>
       <c r="U260" t="inlineStr"/>
       <c r="V260" t="inlineStr"/>
-      <c r="W260" t="inlineStr"/>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
       <c r="X260" t="inlineStr"/>
       <c r="Y260" t="inlineStr"/>
       <c r="Z260" t="inlineStr"/>
-      <c r="AA260" t="inlineStr">
+      <c r="AA260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr"/>
+      <c r="Q261" t="inlineStr"/>
+      <c r="R261" t="inlineStr"/>
+      <c r="S261" t="inlineStr"/>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>vellorra lymphatic contour face brush</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr"/>
+      <c r="V261" t="inlineStr"/>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr"/>
+      <c r="Y261" t="inlineStr"/>
+      <c r="Z261" t="inlineStr"/>
+      <c r="AA261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr"/>
+      <c r="Q262" t="inlineStr"/>
+      <c r="R262" t="inlineStr"/>
+      <c r="S262" t="inlineStr"/>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>lymphatic contour face brush</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr"/>
+      <c r="V262" t="inlineStr"/>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr"/>
+      <c r="Y262" t="inlineStr"/>
+      <c r="Z262" t="inlineStr"/>
+      <c r="AA262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr"/>
+      <c r="R263" t="inlineStr"/>
+      <c r="S263" t="inlineStr"/>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>glow brush lymphatic</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr"/>
+      <c r="V263" t="inlineStr"/>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr"/>
+      <c r="Y263" t="inlineStr"/>
+      <c r="Z263" t="inlineStr"/>
+      <c r="AA263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr"/>
+      <c r="Q264" t="inlineStr"/>
+      <c r="R264" t="inlineStr"/>
+      <c r="S264" t="inlineStr"/>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>korean lymphatic brush</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr"/>
+      <c r="V264" t="inlineStr"/>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr"/>
+      <c r="Y264" t="inlineStr"/>
+      <c r="Z264" t="inlineStr"/>
+      <c r="AA264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr"/>
+      <c r="Q265" t="inlineStr"/>
+      <c r="R265" t="inlineStr"/>
+      <c r="S265" t="inlineStr"/>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>glow brush for face</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr"/>
+      <c r="V265" t="inlineStr"/>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr"/>
+      <c r="Y265" t="inlineStr"/>
+      <c r="Z265" t="inlineStr"/>
+      <c r="AA265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr"/>
+      <c r="Q266" t="inlineStr"/>
+      <c r="R266" t="inlineStr"/>
+      <c r="S266" t="inlineStr"/>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>counter glow face brush</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr"/>
+      <c r="V266" t="inlineStr"/>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr"/>
+      <c r="Y266" t="inlineStr"/>
+      <c r="Z266" t="inlineStr"/>
+      <c r="AA266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr"/>
+      <c r="Q267" t="inlineStr"/>
+      <c r="R267" t="inlineStr"/>
+      <c r="S267" t="inlineStr"/>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>counterglow face brush</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr"/>
+      <c r="V267" t="inlineStr"/>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr"/>
+      <c r="Y267" t="inlineStr"/>
+      <c r="Z267" t="inlineStr"/>
+      <c r="AA267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr"/>
+      <c r="Q268" t="inlineStr"/>
+      <c r="R268" t="inlineStr"/>
+      <c r="S268" t="inlineStr"/>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>face massager brush</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr"/>
+      <c r="V268" t="inlineStr"/>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr"/>
+      <c r="Y268" t="inlineStr"/>
+      <c r="Z268" t="inlineStr"/>
+      <c r="AA268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr"/>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr"/>
+      <c r="Q269" t="inlineStr"/>
+      <c r="R269" t="inlineStr"/>
+      <c r="S269" t="inlineStr"/>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>contour face brush for lymphatic drainage</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr"/>
+      <c r="V269" t="inlineStr"/>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr"/>
+      <c r="Y269" t="inlineStr"/>
+      <c r="Z269" t="inlineStr"/>
+      <c r="AA269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr"/>
+      <c r="Q270" t="inlineStr"/>
+      <c r="R270" t="inlineStr"/>
+      <c r="S270" t="inlineStr"/>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>lymphatic drainage face brush</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr"/>
+      <c r="V270" t="inlineStr"/>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr"/>
+      <c r="Y270" t="inlineStr"/>
+      <c r="Z270" t="inlineStr"/>
+      <c r="AA270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr"/>
+      <c r="Q271" t="inlineStr"/>
+      <c r="R271" t="inlineStr"/>
+      <c r="S271" t="inlineStr"/>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>lymph brush for face and neck</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr"/>
+      <c r="V271" t="inlineStr"/>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr"/>
+      <c r="Y271" t="inlineStr"/>
+      <c r="Z271" t="inlineStr"/>
+      <c r="AA271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr"/>
+      <c r="Q272" t="inlineStr"/>
+      <c r="R272" t="inlineStr"/>
+      <c r="S272" t="inlineStr"/>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>face brush for lymphatic drainage</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr"/>
+      <c r="V272" t="inlineStr"/>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr"/>
+      <c r="Y272" t="inlineStr"/>
+      <c r="Z272" t="inlineStr"/>
+      <c r="AA272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr"/>
+      <c r="Q273" t="inlineStr"/>
+      <c r="R273" t="inlineStr"/>
+      <c r="S273" t="inlineStr"/>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>soft bristle face brush</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr"/>
+      <c r="V273" t="inlineStr"/>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr"/>
+      <c r="Y273" t="inlineStr"/>
+      <c r="Z273" t="inlineStr"/>
+      <c r="AA273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr"/>
+      <c r="Q274" t="inlineStr"/>
+      <c r="R274" t="inlineStr"/>
+      <c r="S274" t="inlineStr"/>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>lymphatic dry brush for face</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr"/>
+      <c r="V274" t="inlineStr"/>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr"/>
+      <c r="Y274" t="inlineStr"/>
+      <c r="Z274" t="inlineStr"/>
+      <c r="AA274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr"/>
+      <c r="Q275" t="inlineStr"/>
+      <c r="R275" t="inlineStr"/>
+      <c r="S275" t="inlineStr"/>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>face sculpting brush lymphatic</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr"/>
+      <c r="V275" t="inlineStr"/>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr"/>
+      <c r="Y275" t="inlineStr"/>
+      <c r="Z275" t="inlineStr"/>
+      <c r="AA275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr"/>
+      <c r="Q276" t="inlineStr"/>
+      <c r="R276" t="inlineStr"/>
+      <c r="S276" t="inlineStr"/>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>nuvetra contour glow brush</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr"/>
+      <c r="V276" t="inlineStr"/>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr"/>
+      <c r="Y276" t="inlineStr"/>
+      <c r="Z276" t="inlineStr"/>
+      <c r="AA276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr"/>
+      <c r="Q277" t="inlineStr"/>
+      <c r="R277" t="inlineStr"/>
+      <c r="S277" t="inlineStr"/>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>kojeva lymphatic brush face</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr"/>
+      <c r="V277" t="inlineStr"/>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr"/>
+      <c r="Y277" t="inlineStr"/>
+      <c r="Z277" t="inlineStr"/>
+      <c r="AA277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr"/>
+      <c r="Q278" t="inlineStr"/>
+      <c r="R278" t="inlineStr"/>
+      <c r="S278" t="inlineStr"/>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>akei lymphatic brush</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr"/>
+      <c r="V278" t="inlineStr"/>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X278" t="inlineStr"/>
+      <c r="Y278" t="inlineStr"/>
+      <c r="Z278" t="inlineStr"/>
+      <c r="AA278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr"/>
+      <c r="Q279" t="inlineStr"/>
+      <c r="R279" t="inlineStr"/>
+      <c r="S279" t="inlineStr"/>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>koniva face brush</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr"/>
+      <c r="V279" t="inlineStr"/>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr"/>
+      <c r="Y279" t="inlineStr"/>
+      <c r="Z279" t="inlineStr"/>
+      <c r="AA279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr"/>
+      <c r="Q280" t="inlineStr"/>
+      <c r="R280" t="inlineStr"/>
+      <c r="S280" t="inlineStr"/>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>soothesilk facial brush</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr"/>
+      <c r="V280" t="inlineStr"/>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr"/>
+      <c r="Y280" t="inlineStr"/>
+      <c r="Z280" t="inlineStr"/>
+      <c r="AA280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr"/>
+      <c r="Q281" t="inlineStr"/>
+      <c r="R281" t="inlineStr"/>
+      <c r="S281" t="inlineStr"/>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>gua sha facial tools</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr"/>
+      <c r="V281" t="inlineStr"/>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr"/>
+      <c r="Y281" t="inlineStr"/>
+      <c r="Z281" t="inlineStr"/>
+      <c r="AA281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr"/>
+      <c r="Q282" t="inlineStr"/>
+      <c r="R282" t="inlineStr"/>
+      <c r="S282" t="inlineStr"/>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>kojeva lymphatic face brush</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr"/>
+      <c r="V282" t="inlineStr"/>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr"/>
+      <c r="Y282" t="inlineStr"/>
+      <c r="Z282" t="inlineStr"/>
+      <c r="AA282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr"/>
+      <c r="Q283" t="inlineStr"/>
+      <c r="R283" t="inlineStr"/>
+      <c r="S283" t="inlineStr"/>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>kitsch lymphatic contour face brush</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr"/>
+      <c r="V283" t="inlineStr"/>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr"/>
+      <c r="Y283" t="inlineStr"/>
+      <c r="Z283" t="inlineStr"/>
+      <c r="AA283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr"/>
+      <c r="Q284" t="inlineStr"/>
+      <c r="R284" t="inlineStr"/>
+      <c r="S284" t="inlineStr"/>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>facial brush</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr"/>
+      <c r="V284" t="inlineStr"/>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X284" t="inlineStr"/>
+      <c r="Y284" t="inlineStr"/>
+      <c r="Z284" t="inlineStr"/>
+      <c r="AA284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr"/>
+      <c r="Q285" t="inlineStr"/>
+      <c r="R285" t="inlineStr"/>
+      <c r="S285" t="inlineStr"/>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>guasha tool for face</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr"/>
+      <c r="V285" t="inlineStr"/>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X285" t="inlineStr"/>
+      <c r="Y285" t="inlineStr"/>
+      <c r="Z285" t="inlineStr"/>
+      <c r="AA285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
+      <c r="J286" t="inlineStr"/>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr"/>
+      <c r="Q286" t="inlineStr"/>
+      <c r="R286" t="inlineStr"/>
+      <c r="S286" t="inlineStr"/>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>contour brush</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr"/>
+      <c r="V286" t="inlineStr"/>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X286" t="inlineStr"/>
+      <c r="Y286" t="inlineStr"/>
+      <c r="Z286" t="inlineStr"/>
+      <c r="AA286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr"/>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr"/>
+      <c r="Q287" t="inlineStr"/>
+      <c r="R287" t="inlineStr"/>
+      <c r="S287" t="inlineStr"/>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>face mask brush</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr"/>
+      <c r="V287" t="inlineStr"/>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
+      </c>
+      <c r="X287" t="inlineStr"/>
+      <c r="Y287" t="inlineStr"/>
+      <c r="Z287" t="inlineStr"/>
+      <c r="AA287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
+      <c r="J288" t="inlineStr"/>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr"/>
+      <c r="Q288" t="inlineStr"/>
+      <c r="R288" t="inlineStr"/>
+      <c r="S288" t="inlineStr"/>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr"/>
+      <c r="V288" t="inlineStr"/>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr"/>
+      <c r="Y288" t="inlineStr"/>
+      <c r="Z288" t="inlineStr"/>
+      <c r="AA288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr"/>
+      <c r="Q289" t="inlineStr"/>
+      <c r="R289" t="inlineStr"/>
+      <c r="S289" t="inlineStr"/>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>makeup</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr"/>
+      <c r="V289" t="inlineStr"/>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+      <c r="X289" t="inlineStr"/>
+      <c r="Y289" t="inlineStr"/>
+      <c r="Z289" t="inlineStr"/>
+      <c r="AA289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr"/>
+      <c r="Q290" t="inlineStr"/>
+      <c r="R290" t="inlineStr"/>
+      <c r="S290" t="inlineStr"/>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr"/>
+      <c r="V290" t="inlineStr"/>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+      <c r="X290" t="inlineStr"/>
+      <c r="Y290" t="inlineStr"/>
+      <c r="Z290" t="inlineStr"/>
+      <c r="AA290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
+      <c r="J291" t="inlineStr"/>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr"/>
+      <c r="Q291" t="inlineStr"/>
+      <c r="R291" t="inlineStr"/>
+      <c r="S291" t="inlineStr"/>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>drops</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr"/>
+      <c r="V291" t="inlineStr"/>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+      <c r="X291" t="inlineStr"/>
+      <c r="Y291" t="inlineStr"/>
+      <c r="Z291" t="inlineStr"/>
+      <c r="AA291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
+      <c r="J292" t="inlineStr"/>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr"/>
+      <c r="Q292" t="inlineStr"/>
+      <c r="R292" t="inlineStr"/>
+      <c r="S292" t="inlineStr"/>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>supplement</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr"/>
+      <c r="V292" t="inlineStr"/>
+      <c r="W292" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+      <c r="X292" t="inlineStr"/>
+      <c r="Y292" t="inlineStr"/>
+      <c r="Z292" t="inlineStr"/>
+      <c r="AA292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr"/>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr"/>
+      <c r="Q293" t="inlineStr"/>
+      <c r="R293" t="inlineStr"/>
+      <c r="S293" t="inlineStr"/>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>pills</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr"/>
+      <c r="V293" t="inlineStr"/>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+      <c r="X293" t="inlineStr"/>
+      <c r="Y293" t="inlineStr"/>
+      <c r="Z293" t="inlineStr"/>
+      <c r="AA293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
+      <c r="J294" t="inlineStr"/>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr"/>
+      <c r="Q294" t="inlineStr"/>
+      <c r="R294" t="inlineStr"/>
+      <c r="S294" t="inlineStr"/>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>toothbrush</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr"/>
+      <c r="V294" t="inlineStr"/>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+      <c r="X294" t="inlineStr"/>
+      <c r="Y294" t="inlineStr"/>
+      <c r="Z294" t="inlineStr"/>
+      <c r="AA294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
+      <c r="J295" t="inlineStr"/>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr"/>
+      <c r="Q295" t="inlineStr"/>
+      <c r="R295" t="inlineStr"/>
+      <c r="S295" t="inlineStr"/>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>cleansing</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr"/>
+      <c r="V295" t="inlineStr"/>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+      <c r="X295" t="inlineStr"/>
+      <c r="Y295" t="inlineStr"/>
+      <c r="Z295" t="inlineStr"/>
+      <c r="AA295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr"/>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr"/>
+      <c r="Q296" t="inlineStr"/>
+      <c r="R296" t="inlineStr"/>
+      <c r="S296" t="inlineStr"/>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>exfoliating</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr"/>
+      <c r="V296" t="inlineStr"/>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+      <c r="X296" t="inlineStr"/>
+      <c r="Y296" t="inlineStr"/>
+      <c r="Z296" t="inlineStr"/>
+      <c r="AA296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
+      <c r="J297" t="inlineStr"/>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr"/>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr"/>
+      <c r="Q297" t="inlineStr"/>
+      <c r="R297" t="inlineStr"/>
+      <c r="S297" t="inlineStr"/>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>powder</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr"/>
+      <c r="V297" t="inlineStr"/>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+      <c r="X297" t="inlineStr"/>
+      <c r="Y297" t="inlineStr"/>
+      <c r="Z297" t="inlineStr"/>
+      <c r="AA297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
+      <c r="J298" t="inlineStr"/>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr"/>
+      <c r="Q298" t="inlineStr"/>
+      <c r="R298" t="inlineStr"/>
+      <c r="S298" t="inlineStr"/>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>ice roller</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr"/>
+      <c r="V298" t="inlineStr"/>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+      <c r="X298" t="inlineStr"/>
+      <c r="Y298" t="inlineStr"/>
+      <c r="Z298" t="inlineStr"/>
+      <c r="AA298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
+      <c r="J299" t="inlineStr"/>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr"/>
+      <c r="Q299" t="inlineStr"/>
+      <c r="R299" t="inlineStr"/>
+      <c r="S299" t="inlineStr"/>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>foundation</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr"/>
+      <c r="V299" t="inlineStr"/>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+      <c r="X299" t="inlineStr"/>
+      <c r="Y299" t="inlineStr"/>
+      <c r="Z299" t="inlineStr"/>
+      <c r="AA299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
+      <c r="J300" t="inlineStr"/>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr"/>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr"/>
+      <c r="Q300" t="inlineStr"/>
+      <c r="R300" t="inlineStr"/>
+      <c r="S300" t="inlineStr"/>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>peel</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr"/>
+      <c r="V300" t="inlineStr"/>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+      <c r="X300" t="inlineStr"/>
+      <c r="Y300" t="inlineStr"/>
+      <c r="Z300" t="inlineStr"/>
+      <c r="AA300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Negative Product Targeting</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
+      <c r="J301" t="inlineStr"/>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr"/>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr"/>
+      <c r="Q301" t="inlineStr"/>
+      <c r="R301" t="inlineStr"/>
+      <c r="S301" t="inlineStr"/>
+      <c r="T301" t="inlineStr"/>
+      <c r="U301" t="inlineStr"/>
+      <c r="V301" t="inlineStr"/>
+      <c r="W301" t="inlineStr"/>
+      <c r="X301" t="inlineStr"/>
+      <c r="Y301" t="inlineStr"/>
+      <c r="Z301" t="inlineStr"/>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>asin="B0FD354L27"</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Negative Product Targeting</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
+      <c r="J302" t="inlineStr"/>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr"/>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr"/>
+      <c r="Q302" t="inlineStr"/>
+      <c r="R302" t="inlineStr"/>
+      <c r="S302" t="inlineStr"/>
+      <c r="T302" t="inlineStr"/>
+      <c r="U302" t="inlineStr"/>
+      <c r="V302" t="inlineStr"/>
+      <c r="W302" t="inlineStr"/>
+      <c r="X302" t="inlineStr"/>
+      <c r="Y302" t="inlineStr"/>
+      <c r="Z302" t="inlineStr"/>
+      <c r="AA302" t="inlineStr">
         <is>
           <t>asin="B0FD6Y9BX5"</t>
         </is>

--- a/Trabajo/E-commerce/Amazon/AVIE/AVIE_OCT_bulk_carga.xlsx
+++ b/Trabajo/E-commerce/Amazon/AVIE/AVIE_OCT_bulk_carga.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA302"/>
+  <dimension ref="A1:AA306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,7 +571,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AVIE_OCT_PROBADAS_EX</t>
+          <t>AVIE_OCT_EMPUJE_EX</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -581,7 +581,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AVIE_OCT_PROBADAS_EX</t>
+          <t>AVIE_OCT_EMPUJE_EX</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AVIE_OCT_PROBADAS_EX</t>
+          <t>AVIE_OCT_EMPUJE_EX</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="inlineStr"/>
     </row>
@@ -689,12 +689,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AVIE_OCT_PROBADAS_EX</t>
+          <t>AVIE_OCT_EMPUJE_EX</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>avie_oct_probadas_ex</t>
+          <t>avie_oct_empuje_ex</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -704,7 +704,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>avie_oct_probadas_ex</t>
+          <t>avie_oct_empuje_ex</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -718,7 +718,7 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -748,12 +748,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AVIE_OCT_PROBADAS_EX</t>
+          <t>AVIE_OCT_EMPUJE_EX</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>avie_oct_probadas_ex</t>
+          <t>avie_oct_empuje_ex</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -805,12 +805,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AVIE_OCT_PROBADAS_EX</t>
+          <t>AVIE_OCT_EMPUJE_EX</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>avie_oct_probadas_ex</t>
+          <t>avie_oct_empuje_ex</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -832,12 +832,12 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>dry brush for lymphatic drainage</t>
+          <t>gua sha brush</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -870,12 +870,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AVIE_OCT_PROBADAS_EX</t>
+          <t>AVIE_OCT_EMPUJE_EX</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>avie_oct_probadas_ex</t>
+          <t>avie_oct_empuje_ex</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -897,12 +897,12 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>lymphatic drainage brush</t>
+          <t>guasha brush for face</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -935,12 +935,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AVIE_OCT_PROBADAS_EX</t>
+          <t>AVIE_OCT_EMPUJE_EX</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>avie_oct_probadas_ex</t>
+          <t>avie_oct_empuje_ex</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -962,12 +962,12 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>lymphatic face brush</t>
+          <t>guasha brush</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AVIE_OCT_PROBADAS_EX</t>
+          <t>AVIE_OCT_EMPUJE_EX</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>avie_oct_probadas_ex</t>
+          <t>avie_oct_empuje_ex</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1027,12 +1027,12 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>face lymphatic drainage brush</t>
+          <t>gua sha brush for face</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AVIE_OCT_PROBADAS_EX</t>
+          <t>AVIE_OCT_EMPUJE_EX</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>avie_oct_probadas_ex</t>
+          <t>avie_oct_empuje_ex</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1092,12 +1092,12 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>lymphatic drainage brush for face</t>
+          <t>contour glow brush</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AVIE_OCT_PROBADAS_EX</t>
+          <t>AVIE_OCT_EMPUJE_EX</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>avie_oct_probadas_ex</t>
+          <t>avie_oct_empuje_ex</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1157,12 +1157,12 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>facial lymphatic drainage brush</t>
+          <t>contour glow face brush</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AVIE_OCT_PROBADAS_EX</t>
+          <t>AVIE_OCT_EMPUJE_EX</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>avie_oct_probadas_ex</t>
+          <t>avie_oct_empuje_ex</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1222,12 +1222,12 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>facial brush for lymphatic drainage</t>
+          <t>contour glow brush for face</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1263,46 +1263,48 @@
           <t>AVIE_OCT_PROBADAS_EX</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>avie_oct_probadas_ex</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_PROBADAS_EX</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>12</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>guasha brush for face</t>
-        </is>
-      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
@@ -1315,7 +1317,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Bidding Adjustment</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1328,11 +1330,7 @@
           <t>AVIE_OCT_PROBADAS_EX</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>avie_oct_probadas_ex</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -1342,34 +1340,24 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>guasha brush</t>
-        </is>
-      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Placement Top</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>30</v>
+      </c>
       <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1380,7 +1368,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1403,7 +1391,11 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>avie_oct_probadas_ex</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -1414,24 +1406,14 @@
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>gua sha brush</t>
-        </is>
-      </c>
+      <c r="R15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
@@ -1445,7 +1427,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1478,25 +1460,17 @@
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>avie 011</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>gua sha brush for face</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
@@ -1552,7 +1526,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>lymphatic drainage brushes</t>
+          <t>dry brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -1617,7 +1591,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>facial lymphatic brush</t>
+          <t>lymphatic drainage brush</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -1682,7 +1656,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>dry face brush for lymphatic drainage</t>
+          <t>lymphatic face brush</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -1747,7 +1721,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>pink lymphatic drainage brush</t>
+          <t>face lymphatic drainage brush</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -1812,7 +1786,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>pink lymphatic contour face brush</t>
+          <t>lymphatic drainage brush for face</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -1877,7 +1851,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>pink lymphatic face brush</t>
+          <t>facial lymphatic drainage brush</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -1937,12 +1911,12 @@
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush</t>
+          <t>facial brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -1965,7 +1939,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1975,51 +1949,49 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AVIE_OCT_QUICKWIN_EX</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>AVIE_OCT_PROBADAS_EX</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>avie_oct_probadas_ex</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>AVIE_OCT_QUICKWIN_EX</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P24" t="n">
-        <v>7</v>
-      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>lymphatic drainage brushes</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Dynamic bids - down only</t>
-        </is>
-      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
@@ -2032,7 +2004,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2042,12 +2014,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AVIE_OCT_QUICKWIN_EX</t>
+          <t>AVIE_OCT_PROBADAS_EX</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>avie_oct_quickwin_ex</t>
+          <t>avie_oct_probadas_ex</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2055,11 +2027,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>avie_oct_quickwin_ex</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -2070,14 +2038,24 @@
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>facial lymphatic brush</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
@@ -2091,7 +2069,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2101,12 +2079,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AVIE_OCT_QUICKWIN_EX</t>
+          <t>AVIE_OCT_PROBADAS_EX</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>avie_oct_quickwin_ex</t>
+          <t>avie_oct_probadas_ex</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2124,17 +2102,25 @@
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>avie 011</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>dry face brush for lymphatic drainage</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
@@ -2158,12 +2144,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AVIE_OCT_QUICKWIN_EX</t>
+          <t>AVIE_OCT_PROBADAS_EX</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>avie_oct_quickwin_ex</t>
+          <t>avie_oct_probadas_ex</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2185,12 +2171,12 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>skin brush for face</t>
+          <t>pink lymphatic drainage brush</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -2223,12 +2209,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AVIE_OCT_QUICKWIN_EX</t>
+          <t>AVIE_OCT_PROBADAS_EX</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>avie_oct_quickwin_ex</t>
+          <t>avie_oct_probadas_ex</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -2250,12 +2236,12 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>soft guasha facial brush</t>
+          <t>pink lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -2288,12 +2274,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AVIE_OCT_QUICKWIN_EX</t>
+          <t>AVIE_OCT_PROBADAS_EX</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>avie_oct_quickwin_ex</t>
+          <t>avie_oct_probadas_ex</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -2315,12 +2301,12 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>depuffing brush for face</t>
+          <t>pink lymphatic face brush</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
@@ -2353,12 +2339,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AVIE_OCT_QUICKWIN_EX</t>
+          <t>AVIE_OCT_PROBADAS_EX</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>avie_oct_quickwin_ex</t>
+          <t>avie_oct_probadas_ex</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -2380,12 +2366,12 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>brush for face drainage</t>
+          <t>lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
@@ -2408,7 +2394,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2421,46 +2407,48 @@
           <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>avie_oct_quickwin_ex</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>10</v>
+      </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>lymphatic contour face brush soft bristles</t>
-        </is>
-      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
@@ -2473,7 +2461,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2496,7 +2484,11 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>avie_oct_quickwin_ex</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -2507,24 +2499,14 @@
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>lymphatic drainage brush soft</t>
-        </is>
-      </c>
+      <c r="R32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
@@ -2538,7 +2520,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2571,25 +2553,17 @@
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>avie 011</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>face drainage brush</t>
-        </is>
-      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
+      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
@@ -2645,7 +2619,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>de-bloat face sculpting brush</t>
+          <t>skin brush for face</t>
         </is>
       </c>
       <c r="U34" t="inlineStr"/>
@@ -2710,7 +2684,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>gua sha dry brush</t>
+          <t>soft guasha facial brush</t>
         </is>
       </c>
       <c r="U35" t="inlineStr"/>
@@ -2775,7 +2749,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>face brush gua sha</t>
+          <t>depuffing brush for face</t>
         </is>
       </c>
       <c r="U36" t="inlineStr"/>
@@ -2840,7 +2814,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>gua sha face brush</t>
+          <t>brush for face drainage</t>
         </is>
       </c>
       <c r="U37" t="inlineStr"/>
@@ -2905,7 +2879,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush korean</t>
+          <t>lymphatic contour face brush soft bristles</t>
         </is>
       </c>
       <c r="U38" t="inlineStr"/>
@@ -2970,7 +2944,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>guasha face brush</t>
+          <t>lymphatic drainage brush soft</t>
         </is>
       </c>
       <c r="U39" t="inlineStr"/>
@@ -3035,7 +3009,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>face brushes for lymphatic drainage</t>
+          <t>face drainage brush</t>
         </is>
       </c>
       <c r="U40" t="inlineStr"/>
@@ -3100,7 +3074,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>brush guasha for face</t>
+          <t>de-bloat face sculpting brush</t>
         </is>
       </c>
       <c r="U41" t="inlineStr"/>
@@ -3165,7 +3139,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>lymphatic drainage brush face</t>
+          <t>gua sha dry brush</t>
         </is>
       </c>
       <c r="U42" t="inlineStr"/>
@@ -3230,7 +3204,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>gua sha facial brush</t>
+          <t>face brush gua sha</t>
         </is>
       </c>
       <c r="U43" t="inlineStr"/>
@@ -3295,7 +3269,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>lymphatic facial drainage brush</t>
+          <t>gua sha face brush</t>
         </is>
       </c>
       <c r="U44" t="inlineStr"/>
@@ -3360,7 +3334,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>face gua sha brush</t>
+          <t>lymphatic contour face brush korean</t>
         </is>
       </c>
       <c r="U45" t="inlineStr"/>
@@ -3425,7 +3399,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>contour facial brush</t>
+          <t>guasha face brush</t>
         </is>
       </c>
       <c r="U46" t="inlineStr"/>
@@ -3490,7 +3464,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>contour brush lymphatic drainage</t>
+          <t>face brushes for lymphatic drainage</t>
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
@@ -3555,7 +3529,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>facial contour brush lymphatic</t>
+          <t>brush guasha for face</t>
         </is>
       </c>
       <c r="U48" t="inlineStr"/>
@@ -3620,7 +3594,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>lymphatic beauty brush</t>
+          <t>lymphatic drainage brush face</t>
         </is>
       </c>
       <c r="U49" t="inlineStr"/>
@@ -3685,7 +3659,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>gua sha dry brush for face</t>
+          <t>gua sha facial brush</t>
         </is>
       </c>
       <c r="U50" t="inlineStr"/>
@@ -3750,7 +3724,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>facial sculpting brushes for lymphatic drainage</t>
+          <t>lymphatic facial drainage brush</t>
         </is>
       </c>
       <c r="U51" t="inlineStr"/>
@@ -3815,7 +3789,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>lymphatic drainage facial brush</t>
+          <t>face gua sha brush</t>
         </is>
       </c>
       <c r="U52" t="inlineStr"/>
@@ -3880,7 +3854,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush soft</t>
+          <t>contour facial brush</t>
         </is>
       </c>
       <c r="U53" t="inlineStr"/>
@@ -3945,7 +3919,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>lymphatic drain face brush</t>
+          <t>contour brush lymphatic drainage</t>
         </is>
       </c>
       <c r="U54" t="inlineStr"/>
@@ -4010,7 +3984,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>facial sculpting brush</t>
+          <t>facial contour brush lymphatic</t>
         </is>
       </c>
       <c r="U55" t="inlineStr"/>
@@ -4075,7 +4049,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>soft face brush lymphatic</t>
+          <t>lymphatic beauty brush</t>
         </is>
       </c>
       <c r="U56" t="inlineStr"/>
@@ -4140,7 +4114,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>lymphatic drain brush for face</t>
+          <t>gua sha dry brush for face</t>
         </is>
       </c>
       <c r="U57" t="inlineStr"/>
@@ -4205,7 +4179,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>facial brushes for lymphatic drainage</t>
+          <t>facial sculpting brushes for lymphatic drainage</t>
         </is>
       </c>
       <c r="U58" t="inlineStr"/>
@@ -4270,7 +4244,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>lymphatic draining brush for face</t>
+          <t>lymphatic drainage facial brush</t>
         </is>
       </c>
       <c r="U59" t="inlineStr"/>
@@ -4335,7 +4309,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>facial drainage brush</t>
+          <t>lymphatic contour face brush soft</t>
         </is>
       </c>
       <c r="U60" t="inlineStr"/>
@@ -4400,7 +4374,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>sculpt brush for face</t>
+          <t>lymphatic drain face brush</t>
         </is>
       </c>
       <c r="U61" t="inlineStr"/>
@@ -4465,7 +4439,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>korean face lifting brush</t>
+          <t>facial sculpting brush</t>
         </is>
       </c>
       <c r="U62" t="inlineStr"/>
@@ -4530,7 +4504,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>facial lymph drainage brush</t>
+          <t>soft face brush lymphatic</t>
         </is>
       </c>
       <c r="U63" t="inlineStr"/>
@@ -4595,7 +4569,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>lymphatic facial contour brush</t>
+          <t>lymphatic drain brush for face</t>
         </is>
       </c>
       <c r="U64" t="inlineStr"/>
@@ -4660,7 +4634,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>sculpting face brush</t>
+          <t>facial brushes for lymphatic drainage</t>
         </is>
       </c>
       <c r="U65" t="inlineStr"/>
@@ -4725,7 +4699,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>dry lymphatic massage brush for face</t>
+          <t>lymphatic draining brush for face</t>
         </is>
       </c>
       <c r="U66" t="inlineStr"/>
@@ -4790,7 +4764,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>lymphatic contour brush for face</t>
+          <t>facial drainage brush</t>
         </is>
       </c>
       <c r="U67" t="inlineStr"/>
@@ -4855,7 +4829,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>face brush lymphatic drainage</t>
+          <t>sculpt brush for face</t>
         </is>
       </c>
       <c r="U68" t="inlineStr"/>
@@ -4920,7 +4894,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>facial contour brush</t>
+          <t>korean face lifting brush</t>
         </is>
       </c>
       <c r="U69" t="inlineStr"/>
@@ -4985,7 +4959,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>contour lymphatic face brush</t>
+          <t>facial lymph drainage brush</t>
         </is>
       </c>
       <c r="U70" t="inlineStr"/>
@@ -5050,7 +5024,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>dry brush face</t>
+          <t>lymphatic facial contour brush</t>
         </is>
       </c>
       <c r="U71" t="inlineStr"/>
@@ -5115,7 +5089,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>face lymphatic brush</t>
+          <t>sculpting face brush</t>
         </is>
       </c>
       <c r="U72" t="inlineStr"/>
@@ -5180,7 +5154,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>korean brush for face</t>
+          <t>dry lymphatic massage brush for face</t>
         </is>
       </c>
       <c r="U73" t="inlineStr"/>
@@ -5245,7 +5219,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>face lymphatic contour brush</t>
+          <t>lymphatic contour brush for face</t>
         </is>
       </c>
       <c r="U74" t="inlineStr"/>
@@ -5310,7 +5284,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>face massage brush</t>
+          <t>face brush lymphatic drainage</t>
         </is>
       </c>
       <c r="U75" t="inlineStr"/>
@@ -5375,7 +5349,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>dry brush for lymphatic drainage face</t>
+          <t>facial contour brush</t>
         </is>
       </c>
       <c r="U76" t="inlineStr"/>
@@ -5440,7 +5414,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>face lifting brush</t>
+          <t>contour lymphatic face brush</t>
         </is>
       </c>
       <c r="U77" t="inlineStr"/>
@@ -5505,7 +5479,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>depuff brush for face</t>
+          <t>dry brush face</t>
         </is>
       </c>
       <c r="U78" t="inlineStr"/>
@@ -5570,7 +5544,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>face dry brush for lymphatic drainage</t>
+          <t>face lymphatic brush</t>
         </is>
       </c>
       <c r="U79" t="inlineStr"/>
@@ -5635,7 +5609,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>korean lymphatic face brush</t>
+          <t>korean brush for face</t>
         </is>
       </c>
       <c r="U80" t="inlineStr"/>
@@ -5700,7 +5674,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>glow brush lymphatic</t>
+          <t>face lymphatic contour brush</t>
         </is>
       </c>
       <c r="U81" t="inlineStr"/>
@@ -5765,7 +5739,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>korean lymphatic brush</t>
+          <t>face massage brush</t>
         </is>
       </c>
       <c r="U82" t="inlineStr"/>
@@ -5830,7 +5804,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>glow brush for face</t>
+          <t>dry brush for lymphatic drainage face</t>
         </is>
       </c>
       <c r="U83" t="inlineStr"/>
@@ -5895,7 +5869,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>counter glow face brush</t>
+          <t>face lifting brush</t>
         </is>
       </c>
       <c r="U84" t="inlineStr"/>
@@ -5960,7 +5934,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>counterglow face brush</t>
+          <t>depuff brush for face</t>
         </is>
       </c>
       <c r="U85" t="inlineStr"/>
@@ -6025,7 +5999,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>face massager brush</t>
+          <t>face dry brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U86" t="inlineStr"/>
@@ -6090,7 +6064,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>contour face brush for lymphatic drainage</t>
+          <t>korean lymphatic face brush</t>
         </is>
       </c>
       <c r="U87" t="inlineStr"/>
@@ -6150,12 +6124,12 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>lymphatic drainage face brush</t>
+          <t>glow brush lymphatic</t>
         </is>
       </c>
       <c r="U88" t="inlineStr"/>
@@ -6220,7 +6194,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>lymph brush for face and neck</t>
+          <t>korean lymphatic brush</t>
         </is>
       </c>
       <c r="U89" t="inlineStr"/>
@@ -6280,12 +6254,12 @@
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>face brush for lymphatic drainage</t>
+          <t>glow brush for face</t>
         </is>
       </c>
       <c r="U90" t="inlineStr"/>
@@ -6345,12 +6319,12 @@
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>soft bristle face brush</t>
+          <t>counter glow face brush</t>
         </is>
       </c>
       <c r="U91" t="inlineStr"/>
@@ -6410,12 +6384,12 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>lymphatic dry brush for face</t>
+          <t>counterglow face brush</t>
         </is>
       </c>
       <c r="U92" t="inlineStr"/>
@@ -6475,12 +6449,12 @@
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>face sculpting brush lymphatic</t>
+          <t>face massager brush</t>
         </is>
       </c>
       <c r="U93" t="inlineStr"/>
@@ -6503,7 +6477,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6513,51 +6487,49 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>avie_oct_quickwin_ex</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
-        </is>
-      </c>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P94" t="n">
-        <v>2</v>
-      </c>
+      <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>contour face brush for lymphatic drainage</t>
+        </is>
+      </c>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>Dynamic bids - down only</t>
-        </is>
-      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="inlineStr"/>
       <c r="AA94" t="inlineStr"/>
@@ -6570,7 +6542,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6580,12 +6552,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -6593,11 +6565,7 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>avie_oct_rivales_ex</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
@@ -6608,14 +6576,24 @@
       </c>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>lymphatic drainage face brush</t>
+        </is>
+      </c>
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
@@ -6629,7 +6607,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6639,12 +6617,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -6662,17 +6640,25 @@
         </is>
       </c>
       <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>avie 011</t>
-        </is>
-      </c>
+      <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>lymph brush for face and neck</t>
+        </is>
+      </c>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="inlineStr"/>
@@ -6696,12 +6682,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -6723,12 +6709,12 @@
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>contour glow brush for face</t>
+          <t>face brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U97" t="inlineStr"/>
@@ -6761,12 +6747,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -6793,7 +6779,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>k glow face sculpting brush</t>
+          <t>soft bristle face brush</t>
         </is>
       </c>
       <c r="U98" t="inlineStr"/>
@@ -6826,12 +6812,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -6853,12 +6839,12 @@
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>contour glow brush</t>
+          <t>lymphatic dry brush for face</t>
         </is>
       </c>
       <c r="U99" t="inlineStr"/>
@@ -6891,12 +6877,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AVIE_OCT_RIVALES_EX</t>
+          <t>AVIE_OCT_QUICKWIN_EX</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>avie_oct_rivales_ex</t>
+          <t>avie_oct_quickwin_ex</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -6918,12 +6904,12 @@
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush k glow</t>
+          <t>face sculpting brush lymphatic</t>
         </is>
       </c>
       <c r="U100" t="inlineStr"/>
@@ -6946,7 +6932,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6959,46 +6945,48 @@
           <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>avie_oct_rivales_ex</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_RIVALES_EX</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
       <c r="O101" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr"/>
+      <c r="P101" t="n">
+        <v>3</v>
+      </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>contour glow face brush</t>
-        </is>
-      </c>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
+        </is>
+      </c>
       <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="inlineStr"/>
@@ -7011,7 +6999,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7034,7 +7022,11 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>avie_oct_rivales_ex</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
@@ -7045,24 +7037,14 @@
       </c>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>contourglow brush</t>
-        </is>
-      </c>
+      <c r="R102" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
+      <c r="W102" t="inlineStr"/>
       <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
@@ -7076,7 +7058,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7109,25 +7091,17 @@
         </is>
       </c>
       <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>avie 011</t>
+        </is>
+      </c>
       <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>skinn double-ended face massage brush</t>
-        </is>
-      </c>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
+      <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr"/>
@@ -7183,7 +7157,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>nuventra facial brush</t>
+          <t>k glow face sculpting brush</t>
         </is>
       </c>
       <c r="U104" t="inlineStr"/>
@@ -7248,7 +7222,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>face beauty workshop lymphatic brush</t>
+          <t>lymphatic contour face brush k glow</t>
         </is>
       </c>
       <c r="U105" t="inlineStr"/>
@@ -7313,7 +7287,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>koneva lymphatic face brush</t>
+          <t>contourglow brush</t>
         </is>
       </c>
       <c r="U106" t="inlineStr"/>
@@ -7378,7 +7352,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>floriem lymphatic face brush</t>
+          <t>skinn double-ended face massage brush</t>
         </is>
       </c>
       <c r="U107" t="inlineStr"/>
@@ -7443,7 +7417,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>auvorra lymphatic contour face brush</t>
+          <t>nuventra facial brush</t>
         </is>
       </c>
       <c r="U108" t="inlineStr"/>
@@ -7508,7 +7482,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>kojeca lymphatic face brush</t>
+          <t>face beauty workshop lymphatic brush</t>
         </is>
       </c>
       <c r="U109" t="inlineStr"/>
@@ -7573,7 +7547,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>nuevetra face brush</t>
+          <t>koneva lymphatic face brush</t>
         </is>
       </c>
       <c r="U110" t="inlineStr"/>
@@ -7638,7 +7612,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>kogeva lymphatic face brush</t>
+          <t>floriem lymphatic face brush</t>
         </is>
       </c>
       <c r="U111" t="inlineStr"/>
@@ -7703,7 +7677,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>cecily braden lymphatic face brush</t>
+          <t>auvorra lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U112" t="inlineStr"/>
@@ -7768,7 +7742,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>soothesilk facial contour brush</t>
+          <t>kojeca lymphatic face brush</t>
         </is>
       </c>
       <c r="U113" t="inlineStr"/>
@@ -7833,7 +7807,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>sefvako lymphatic contour face brush</t>
+          <t>nuevetra face brush</t>
         </is>
       </c>
       <c r="U114" t="inlineStr"/>
@@ -7898,7 +7872,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>recuvia lymphatic contour face brush eliminate puffiness in minutes</t>
+          <t>kogeva lymphatic face brush</t>
         </is>
       </c>
       <c r="U115" t="inlineStr"/>
@@ -7963,7 +7937,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>vough lymphatic contour face brush</t>
+          <t>cecily braden lymphatic face brush</t>
         </is>
       </c>
       <c r="U116" t="inlineStr"/>
@@ -8028,7 +8002,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>akei lymphatic facial brush</t>
+          <t>soothesilk facial contour brush</t>
         </is>
       </c>
       <c r="U117" t="inlineStr"/>
@@ -8093,7 +8067,7 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>aeli lymphatic face brush</t>
+          <t>sefvako lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U118" t="inlineStr"/>
@@ -8158,7 +8132,7 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush puur house</t>
+          <t>recuvia lymphatic contour face brush eliminate puffiness in minutes</t>
         </is>
       </c>
       <c r="U119" t="inlineStr"/>
@@ -8223,7 +8197,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>koje a lymphatic face brush</t>
+          <t>vough lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U120" t="inlineStr"/>
@@ -8288,7 +8262,7 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>koheva lymphatic face brush</t>
+          <t>akei lymphatic facial brush</t>
         </is>
       </c>
       <c r="U121" t="inlineStr"/>
@@ -8353,7 +8327,7 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>awki lymphatic face brush</t>
+          <t>aeli lymphatic face brush</t>
         </is>
       </c>
       <c r="U122" t="inlineStr"/>
@@ -8418,7 +8392,7 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>kojovia face brush for lymphatic drainage</t>
+          <t>lymphatic contour face brush puur house</t>
         </is>
       </c>
       <c r="U123" t="inlineStr"/>
@@ -8483,7 +8457,7 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>arki lymphatic face brush</t>
+          <t>koje a lymphatic face brush</t>
         </is>
       </c>
       <c r="U124" t="inlineStr"/>
@@ -8548,7 +8522,7 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>puur house lymphatic contour face brush</t>
+          <t>koheva lymphatic face brush</t>
         </is>
       </c>
       <c r="U125" t="inlineStr"/>
@@ -8613,7 +8587,7 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>lymphatic brush by cecily braden</t>
+          <t>awki lymphatic face brush</t>
         </is>
       </c>
       <c r="U126" t="inlineStr"/>
@@ -8678,7 +8652,7 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>kojevs lymphatic face brush</t>
+          <t>kojovia face brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U127" t="inlineStr"/>
@@ -8743,7 +8717,7 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>eteross lymphatic face brush</t>
+          <t>arki lymphatic face brush</t>
         </is>
       </c>
       <c r="U128" t="inlineStr"/>
@@ -8808,7 +8782,7 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>vddo lymphatic contour face brush</t>
+          <t>puur house lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U129" t="inlineStr"/>
@@ -8873,7 +8847,7 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>vellorra lymphatic contour face brush</t>
+          <t>lymphatic brush by cecily braden</t>
         </is>
       </c>
       <c r="U130" t="inlineStr"/>
@@ -8938,7 +8912,7 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>nuvetra contour glow brush</t>
+          <t>kojevs lymphatic face brush</t>
         </is>
       </c>
       <c r="U131" t="inlineStr"/>
@@ -9003,7 +8977,7 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>kojeva lymphatic brush face</t>
+          <t>eteross lymphatic face brush</t>
         </is>
       </c>
       <c r="U132" t="inlineStr"/>
@@ -9068,7 +9042,7 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>akei lymphatic brush</t>
+          <t>vddo lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U133" t="inlineStr"/>
@@ -9133,7 +9107,7 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>koniva face brush</t>
+          <t>vellorra lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U134" t="inlineStr"/>
@@ -9198,7 +9172,7 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>soothesilk facial brush</t>
+          <t>nuvetra contour glow brush</t>
         </is>
       </c>
       <c r="U135" t="inlineStr"/>
@@ -9221,7 +9195,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9231,51 +9205,49 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>AVIE_OCT_ASIN</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
+          <t>AVIE_OCT_RIVALES_EX</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>avie_oct_rivales_ex</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>AVIE_OCT_ASIN</t>
-        </is>
-      </c>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
+      <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P136" t="n">
-        <v>3</v>
-      </c>
+      <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
-      <c r="T136" t="inlineStr"/>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>kojeva lymphatic brush face</t>
+        </is>
+      </c>
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr"/>
-      <c r="W136" t="inlineStr"/>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>Dynamic bids - down only</t>
-        </is>
-      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr"/>
       <c r="Z136" t="inlineStr"/>
       <c r="AA136" t="inlineStr"/>
@@ -9288,7 +9260,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9298,12 +9270,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>AVIE_OCT_ASIN</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>avie_oct_asin</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -9311,11 +9283,7 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>avie_oct_asin</t>
-        </is>
-      </c>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
@@ -9326,14 +9294,24 @@
       </c>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
-      <c r="R137" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="S137" t="inlineStr"/>
-      <c r="T137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>akei lymphatic brush</t>
+        </is>
+      </c>
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
-      <c r="W137" t="inlineStr"/>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr"/>
       <c r="Z137" t="inlineStr"/>
@@ -9347,7 +9325,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9357,12 +9335,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>AVIE_OCT_ASIN</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>avie_oct_asin</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -9380,17 +9358,25 @@
         </is>
       </c>
       <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>avie 011</t>
-        </is>
-      </c>
+      <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
-      <c r="T138" t="inlineStr"/>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>koniva face brush</t>
+        </is>
+      </c>
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr"/>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" t="inlineStr"/>
@@ -9404,7 +9390,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Product Targeting</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9414,12 +9400,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AVIE_OCT_ASIN</t>
+          <t>AVIE_OCT_RIVALES_EX</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>avie_oct_asin</t>
+          <t>avie_oct_rivales_ex</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -9441,21 +9427,25 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="T139" t="inlineStr"/>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>soothesilk facial brush</t>
+        </is>
+      </c>
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
-      <c r="W139" t="inlineStr"/>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="inlineStr"/>
-      <c r="AA139" t="inlineStr">
-        <is>
-          <t>asin="B0GFSMWTPK"</t>
-        </is>
-      </c>
+      <c r="AA139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9465,7 +9455,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Product Targeting</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9478,45 +9468,51 @@
           <t>AVIE_OCT_ASIN</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>avie_oct_asin</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_ASIN</t>
+        </is>
+      </c>
       <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
       <c r="O140" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P140" t="inlineStr"/>
+      <c r="P140" t="n">
+        <v>4</v>
+      </c>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
+      <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr"/>
       <c r="W140" t="inlineStr"/>
-      <c r="X140" t="inlineStr"/>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
+        </is>
+      </c>
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="inlineStr"/>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>asin="B0GVBQ7P79"</t>
-        </is>
-      </c>
+      <c r="AA140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9526,7 +9522,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Product Targeting</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9549,7 +9545,11 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>avie_oct_asin</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
@@ -9560,12 +9560,10 @@
       </c>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
-      <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
+      <c r="R141" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
@@ -9573,11 +9571,7 @@
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr"/>
       <c r="Z141" t="inlineStr"/>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>asin="B0G3685P2S"</t>
-        </is>
-      </c>
+      <c r="AA141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9587,7 +9581,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9597,51 +9591,41 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>AVIE_OCT_DESCUBRIR_PH</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
+          <t>AVIE_OCT_ASIN</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>avie_oct_asin</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>AVIE_OCT_DESCUBRIR_PH</t>
-        </is>
-      </c>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
+      <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P142" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>avie 011</t>
+        </is>
+      </c>
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
       <c r="W142" t="inlineStr"/>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>Dynamic bids - down only</t>
-        </is>
-      </c>
+      <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr"/>
       <c r="Z142" t="inlineStr"/>
       <c r="AA142" t="inlineStr"/>
@@ -9654,7 +9638,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9664,12 +9648,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>AVIE_OCT_DESCUBRIR_PH</t>
+          <t>AVIE_OCT_ASIN</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>avie_oct_descubrir_ph</t>
+          <t>avie_oct_asin</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -9677,11 +9661,7 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>avie_oct_descubrir_ph</t>
-        </is>
-      </c>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
@@ -9692,10 +9672,12 @@
       </c>
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
-      <c r="R143" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="S143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
@@ -9703,7 +9685,11 @@
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr"/>
       <c r="Z143" t="inlineStr"/>
-      <c r="AA143" t="inlineStr"/>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>asin="B0GFSMWTPK"</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9713,7 +9699,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9723,12 +9709,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>AVIE_OCT_DESCUBRIR_PH</t>
+          <t>AVIE_OCT_ASIN</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>avie_oct_descubrir_ph</t>
+          <t>avie_oct_asin</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -9746,13 +9732,13 @@
         </is>
       </c>
       <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>avie 011</t>
-        </is>
-      </c>
+      <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
-      <c r="S144" t="inlineStr"/>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
       <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
@@ -9760,7 +9746,11 @@
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" t="inlineStr"/>
-      <c r="AA144" t="inlineStr"/>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>asin="B0GVBQ7P79"</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9770,7 +9760,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9780,12 +9770,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>AVIE_OCT_DESCUBRIR_PH</t>
+          <t>AVIE_OCT_ASIN</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>avie_oct_descubrir_ph</t>
+          <t>avie_oct_asin</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -9807,25 +9797,21 @@
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="T145" t="inlineStr">
-        <is>
-          <t>lymphatic face brush</t>
-        </is>
-      </c>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
-      </c>
+      <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr"/>
       <c r="Z145" t="inlineStr"/>
-      <c r="AA145" t="inlineStr"/>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>asin="B0G3685P2S"</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9835,7 +9821,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9848,46 +9834,48 @@
           <t>AVIE_OCT_DESCUBRIR_PH</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>avie_oct_descubrir_ph</t>
-        </is>
-      </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_DESCUBRIR_PH</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
       <c r="O146" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P146" t="inlineStr"/>
+      <c r="P146" t="n">
+        <v>3</v>
+      </c>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="T146" t="inlineStr">
-        <is>
-          <t>lymphatic drainage brush</t>
-        </is>
-      </c>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr"/>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
-      </c>
-      <c r="X146" t="inlineStr"/>
+      <c r="W146" t="inlineStr"/>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
+        </is>
+      </c>
       <c r="Y146" t="inlineStr"/>
       <c r="Z146" t="inlineStr"/>
       <c r="AA146" t="inlineStr"/>
@@ -9900,7 +9888,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9923,7 +9911,11 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>avie_oct_descubrir_ph</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
@@ -9934,24 +9926,14 @@
       </c>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
-      <c r="R147" t="inlineStr"/>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="T147" t="inlineStr">
-        <is>
-          <t>gua sha brush</t>
-        </is>
-      </c>
+      <c r="R147" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr"/>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
-      </c>
+      <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="inlineStr"/>
@@ -9965,7 +9947,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9998,25 +9980,17 @@
         </is>
       </c>
       <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>avie 011</t>
+        </is>
+      </c>
       <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>face sculpting brush</t>
-        </is>
-      </c>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr"/>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
-      </c>
+      <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr"/>
       <c r="Z148" t="inlineStr"/>
@@ -10072,7 +10046,7 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>depuff brush</t>
+          <t>lymphatic face brush</t>
         </is>
       </c>
       <c r="U149" t="inlineStr"/>
@@ -10095,7 +10069,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -10105,51 +10079,49 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
+          <t>AVIE_OCT_DESCUBRIR_PH</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>avie_oct_descubrir_ph</t>
+        </is>
+      </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
-        </is>
-      </c>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
+      <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="P150" t="n">
-        <v>3</v>
-      </c>
+      <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr"/>
-      <c r="T150" t="inlineStr"/>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>lymphatic drainage brush</t>
+        </is>
+      </c>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr"/>
-      <c r="W150" t="inlineStr"/>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>Dynamic bids - down only</t>
-        </is>
-      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr"/>
       <c r="Z150" t="inlineStr"/>
       <c r="AA150" t="inlineStr"/>
@@ -10162,7 +10134,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10172,12 +10144,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_DESCUBRIR_PH</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_descubrir_ph</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -10185,11 +10157,7 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>avie_oct_auto_cosecha</t>
-        </is>
-      </c>
+      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
@@ -10200,14 +10168,24 @@
       </c>
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
-      <c r="R151" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S151" t="inlineStr"/>
-      <c r="T151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>gua sha brush</t>
+        </is>
+      </c>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr"/>
-      <c r="W151" t="inlineStr"/>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr"/>
       <c r="Z151" t="inlineStr"/>
@@ -10221,7 +10199,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -10231,12 +10209,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_DESCUBRIR_PH</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_descubrir_ph</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -10254,17 +10232,25 @@
         </is>
       </c>
       <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>avie 011</t>
-        </is>
-      </c>
+      <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr"/>
-      <c r="T152" t="inlineStr"/>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>face sculpting brush</t>
+        </is>
+      </c>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
-      <c r="W152" t="inlineStr"/>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="inlineStr"/>
@@ -10278,7 +10264,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Product Targeting</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10288,12 +10274,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>AVIE_OCT_AUTO_COSECHA</t>
+          <t>AVIE_OCT_DESCUBRIR_PH</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>avie_oct_auto_cosecha</t>
+          <t>avie_oct_descubrir_ph</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -10315,21 +10301,25 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="T153" t="inlineStr"/>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>depuff brush</t>
+        </is>
+      </c>
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr"/>
-      <c r="W153" t="inlineStr"/>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr"/>
       <c r="Z153" t="inlineStr"/>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>loose-match</t>
-        </is>
-      </c>
+      <c r="AA153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10339,7 +10329,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Product Targeting</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -10352,43 +10342,51 @@
           <t>AVIE_OCT_AUTO_COSECHA</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>avie_oct_auto_cosecha</t>
-        </is>
-      </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
       <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
       <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>paused</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr"/>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>3</v>
+      </c>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
-      <c r="S154" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
       <c r="W154" t="inlineStr"/>
-      <c r="X154" t="inlineStr"/>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
+        </is>
+      </c>
       <c r="Y154" t="inlineStr"/>
       <c r="Z154" t="inlineStr"/>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>close-match</t>
-        </is>
-      </c>
+      <c r="AA154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10398,7 +10396,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Product Targeting</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10421,21 +10419,25 @@
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
-          <t>paused</t>
+          <t>enabled</t>
         </is>
       </c>
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
-      <c r="R155" t="inlineStr"/>
-      <c r="S155" t="n">
+      <c r="R155" t="n">
         <v>0.4</v>
       </c>
+      <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr"/>
@@ -10443,11 +10445,7 @@
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr"/>
       <c r="Z155" t="inlineStr"/>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>substitutes</t>
-        </is>
-      </c>
+      <c r="AA155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10457,7 +10455,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Product Targeting</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10486,15 +10484,17 @@
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr">
         <is>
-          <t>paused</t>
+          <t>enabled</t>
         </is>
       </c>
       <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>avie 011</t>
+        </is>
+      </c>
       <c r="R156" t="inlineStr"/>
-      <c r="S156" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr"/>
@@ -10502,11 +10502,7 @@
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr"/>
       <c r="Z156" t="inlineStr"/>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>complements</t>
-        </is>
-      </c>
+      <c r="AA156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10516,7 +10512,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10551,23 +10547,23 @@
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr"/>
-      <c r="T157" t="inlineStr">
-        <is>
-          <t>dry brush for lymphatic drainage</t>
-        </is>
-      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr"/>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W157" t="inlineStr"/>
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr"/>
       <c r="Z157" t="inlineStr"/>
-      <c r="AA157" t="inlineStr"/>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>loose-match</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10577,7 +10573,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10606,29 +10602,27 @@
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>paused</t>
         </is>
       </c>
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr"/>
-      <c r="T158" t="inlineStr">
-        <is>
-          <t>lymphatic drainage brush</t>
-        </is>
-      </c>
+      <c r="S158" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr"/>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W158" t="inlineStr"/>
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="inlineStr"/>
       <c r="Z158" t="inlineStr"/>
-      <c r="AA158" t="inlineStr"/>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>close-match</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10638,7 +10632,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10667,29 +10661,27 @@
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>paused</t>
         </is>
       </c>
       <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr"/>
-      <c r="S159" t="inlineStr"/>
-      <c r="T159" t="inlineStr">
-        <is>
-          <t>lymphatic face brush</t>
-        </is>
-      </c>
+      <c r="S159" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr"/>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W159" t="inlineStr"/>
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr"/>
       <c r="Z159" t="inlineStr"/>
-      <c r="AA159" t="inlineStr"/>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>substitutes</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10699,7 +10691,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10728,29 +10720,27 @@
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>paused</t>
         </is>
       </c>
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr"/>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t>face lymphatic drainage brush</t>
-        </is>
-      </c>
+      <c r="S160" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr"/>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>negativeExact</t>
-        </is>
-      </c>
+      <c r="W160" t="inlineStr"/>
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr"/>
       <c r="Z160" t="inlineStr"/>
-      <c r="AA160" t="inlineStr"/>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>complements</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10798,7 +10788,7 @@
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr">
         <is>
-          <t>lymphatic drainage brush for face</t>
+          <t>dry brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U161" t="inlineStr"/>
@@ -10859,7 +10849,7 @@
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr">
         <is>
-          <t>facial lymphatic drainage brush</t>
+          <t>lymphatic drainage brush</t>
         </is>
       </c>
       <c r="U162" t="inlineStr"/>
@@ -10920,7 +10910,7 @@
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr">
         <is>
-          <t>facial brush for lymphatic drainage</t>
+          <t>lymphatic face brush</t>
         </is>
       </c>
       <c r="U163" t="inlineStr"/>
@@ -10981,7 +10971,7 @@
       <c r="S164" t="inlineStr"/>
       <c r="T164" t="inlineStr">
         <is>
-          <t>guasha brush for face</t>
+          <t>face lymphatic drainage brush</t>
         </is>
       </c>
       <c r="U164" t="inlineStr"/>
@@ -11042,7 +11032,7 @@
       <c r="S165" t="inlineStr"/>
       <c r="T165" t="inlineStr">
         <is>
-          <t>guasha brush</t>
+          <t>lymphatic drainage brush for face</t>
         </is>
       </c>
       <c r="U165" t="inlineStr"/>
@@ -11103,7 +11093,7 @@
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr">
         <is>
-          <t>gua sha brush</t>
+          <t>facial lymphatic drainage brush</t>
         </is>
       </c>
       <c r="U166" t="inlineStr"/>
@@ -11164,7 +11154,7 @@
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr">
         <is>
-          <t>gua sha brush for face</t>
+          <t>facial brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U167" t="inlineStr"/>
@@ -11225,7 +11215,7 @@
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr">
         <is>
-          <t>lymphatic drainage brushes</t>
+          <t>guasha brush for face</t>
         </is>
       </c>
       <c r="U168" t="inlineStr"/>
@@ -11286,7 +11276,7 @@
       <c r="S169" t="inlineStr"/>
       <c r="T169" t="inlineStr">
         <is>
-          <t>facial lymphatic brush</t>
+          <t>guasha brush</t>
         </is>
       </c>
       <c r="U169" t="inlineStr"/>
@@ -11347,7 +11337,7 @@
       <c r="S170" t="inlineStr"/>
       <c r="T170" t="inlineStr">
         <is>
-          <t>dry face brush for lymphatic drainage</t>
+          <t>gua sha brush</t>
         </is>
       </c>
       <c r="U170" t="inlineStr"/>
@@ -11408,7 +11398,7 @@
       <c r="S171" t="inlineStr"/>
       <c r="T171" t="inlineStr">
         <is>
-          <t>pink lymphatic drainage brush</t>
+          <t>gua sha brush for face</t>
         </is>
       </c>
       <c r="U171" t="inlineStr"/>
@@ -11469,7 +11459,7 @@
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr">
         <is>
-          <t>pink lymphatic contour face brush</t>
+          <t>lymphatic drainage brushes</t>
         </is>
       </c>
       <c r="U172" t="inlineStr"/>
@@ -11530,7 +11520,7 @@
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr">
         <is>
-          <t>pink lymphatic face brush</t>
+          <t>facial lymphatic brush</t>
         </is>
       </c>
       <c r="U173" t="inlineStr"/>
@@ -11591,7 +11581,7 @@
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr">
         <is>
-          <t>skin brush for face</t>
+          <t>dry face brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U174" t="inlineStr"/>
@@ -11652,7 +11642,7 @@
       <c r="S175" t="inlineStr"/>
       <c r="T175" t="inlineStr">
         <is>
-          <t>soft guasha facial brush</t>
+          <t>pink lymphatic drainage brush</t>
         </is>
       </c>
       <c r="U175" t="inlineStr"/>
@@ -11713,7 +11703,7 @@
       <c r="S176" t="inlineStr"/>
       <c r="T176" t="inlineStr">
         <is>
-          <t>depuffing brush for face</t>
+          <t>pink lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U176" t="inlineStr"/>
@@ -11774,7 +11764,7 @@
       <c r="S177" t="inlineStr"/>
       <c r="T177" t="inlineStr">
         <is>
-          <t>brush for face drainage</t>
+          <t>pink lymphatic face brush</t>
         </is>
       </c>
       <c r="U177" t="inlineStr"/>
@@ -11835,7 +11825,7 @@
       <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush soft bristles</t>
+          <t>skin brush for face</t>
         </is>
       </c>
       <c r="U178" t="inlineStr"/>
@@ -11896,7 +11886,7 @@
       <c r="S179" t="inlineStr"/>
       <c r="T179" t="inlineStr">
         <is>
-          <t>lymphatic drainage brush soft</t>
+          <t>soft guasha facial brush</t>
         </is>
       </c>
       <c r="U179" t="inlineStr"/>
@@ -11957,7 +11947,7 @@
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr">
         <is>
-          <t>face drainage brush</t>
+          <t>depuffing brush for face</t>
         </is>
       </c>
       <c r="U180" t="inlineStr"/>
@@ -12018,7 +12008,7 @@
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr">
         <is>
-          <t>de-bloat face sculpting brush</t>
+          <t>brush for face drainage</t>
         </is>
       </c>
       <c r="U181" t="inlineStr"/>
@@ -12079,7 +12069,7 @@
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr">
         <is>
-          <t>gua sha dry brush</t>
+          <t>lymphatic contour face brush soft bristles</t>
         </is>
       </c>
       <c r="U182" t="inlineStr"/>
@@ -12140,7 +12130,7 @@
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr">
         <is>
-          <t>face brush gua sha</t>
+          <t>lymphatic drainage brush soft</t>
         </is>
       </c>
       <c r="U183" t="inlineStr"/>
@@ -12201,7 +12191,7 @@
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr">
         <is>
-          <t>gua sha face brush</t>
+          <t>face drainage brush</t>
         </is>
       </c>
       <c r="U184" t="inlineStr"/>
@@ -12262,7 +12252,7 @@
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush korean</t>
+          <t>de-bloat face sculpting brush</t>
         </is>
       </c>
       <c r="U185" t="inlineStr"/>
@@ -12323,7 +12313,7 @@
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr">
         <is>
-          <t>guasha face brush</t>
+          <t>gua sha dry brush</t>
         </is>
       </c>
       <c r="U186" t="inlineStr"/>
@@ -12384,7 +12374,7 @@
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr">
         <is>
-          <t>face brushes for lymphatic drainage</t>
+          <t>face brush gua sha</t>
         </is>
       </c>
       <c r="U187" t="inlineStr"/>
@@ -12445,7 +12435,7 @@
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr">
         <is>
-          <t>brush guasha for face</t>
+          <t>gua sha face brush</t>
         </is>
       </c>
       <c r="U188" t="inlineStr"/>
@@ -12506,7 +12496,7 @@
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr">
         <is>
-          <t>lymphatic drainage brush face</t>
+          <t>lymphatic contour face brush korean</t>
         </is>
       </c>
       <c r="U189" t="inlineStr"/>
@@ -12567,7 +12557,7 @@
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr">
         <is>
-          <t>gua sha facial brush</t>
+          <t>guasha face brush</t>
         </is>
       </c>
       <c r="U190" t="inlineStr"/>
@@ -12628,7 +12618,7 @@
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr">
         <is>
-          <t>lymphatic facial drainage brush</t>
+          <t>face brushes for lymphatic drainage</t>
         </is>
       </c>
       <c r="U191" t="inlineStr"/>
@@ -12689,7 +12679,7 @@
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr">
         <is>
-          <t>face gua sha brush</t>
+          <t>brush guasha for face</t>
         </is>
       </c>
       <c r="U192" t="inlineStr"/>
@@ -12750,7 +12740,7 @@
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr">
         <is>
-          <t>contour facial brush</t>
+          <t>lymphatic drainage brush face</t>
         </is>
       </c>
       <c r="U193" t="inlineStr"/>
@@ -12811,7 +12801,7 @@
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr">
         <is>
-          <t>contour brush lymphatic drainage</t>
+          <t>gua sha facial brush</t>
         </is>
       </c>
       <c r="U194" t="inlineStr"/>
@@ -12872,7 +12862,7 @@
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr">
         <is>
-          <t>facial contour brush lymphatic</t>
+          <t>lymphatic facial drainage brush</t>
         </is>
       </c>
       <c r="U195" t="inlineStr"/>
@@ -12933,7 +12923,7 @@
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr">
         <is>
-          <t>lymphatic beauty brush</t>
+          <t>face gua sha brush</t>
         </is>
       </c>
       <c r="U196" t="inlineStr"/>
@@ -12994,7 +12984,7 @@
       <c r="S197" t="inlineStr"/>
       <c r="T197" t="inlineStr">
         <is>
-          <t>gua sha dry brush for face</t>
+          <t>contour facial brush</t>
         </is>
       </c>
       <c r="U197" t="inlineStr"/>
@@ -13055,7 +13045,7 @@
       <c r="S198" t="inlineStr"/>
       <c r="T198" t="inlineStr">
         <is>
-          <t>facial sculpting brushes for lymphatic drainage</t>
+          <t>contour brush lymphatic drainage</t>
         </is>
       </c>
       <c r="U198" t="inlineStr"/>
@@ -13116,7 +13106,7 @@
       <c r="S199" t="inlineStr"/>
       <c r="T199" t="inlineStr">
         <is>
-          <t>lymphatic drainage facial brush</t>
+          <t>facial contour brush lymphatic</t>
         </is>
       </c>
       <c r="U199" t="inlineStr"/>
@@ -13177,7 +13167,7 @@
       <c r="S200" t="inlineStr"/>
       <c r="T200" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush soft</t>
+          <t>lymphatic beauty brush</t>
         </is>
       </c>
       <c r="U200" t="inlineStr"/>
@@ -13238,7 +13228,7 @@
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr">
         <is>
-          <t>lymphatic drain face brush</t>
+          <t>gua sha dry brush for face</t>
         </is>
       </c>
       <c r="U201" t="inlineStr"/>
@@ -13299,7 +13289,7 @@
       <c r="S202" t="inlineStr"/>
       <c r="T202" t="inlineStr">
         <is>
-          <t>facial sculpting brush</t>
+          <t>facial sculpting brushes for lymphatic drainage</t>
         </is>
       </c>
       <c r="U202" t="inlineStr"/>
@@ -13360,7 +13350,7 @@
       <c r="S203" t="inlineStr"/>
       <c r="T203" t="inlineStr">
         <is>
-          <t>soft face brush lymphatic</t>
+          <t>lymphatic drainage facial brush</t>
         </is>
       </c>
       <c r="U203" t="inlineStr"/>
@@ -13421,7 +13411,7 @@
       <c r="S204" t="inlineStr"/>
       <c r="T204" t="inlineStr">
         <is>
-          <t>lymphatic drain brush for face</t>
+          <t>lymphatic contour face brush soft</t>
         </is>
       </c>
       <c r="U204" t="inlineStr"/>
@@ -13482,7 +13472,7 @@
       <c r="S205" t="inlineStr"/>
       <c r="T205" t="inlineStr">
         <is>
-          <t>facial brushes for lymphatic drainage</t>
+          <t>lymphatic drain face brush</t>
         </is>
       </c>
       <c r="U205" t="inlineStr"/>
@@ -13543,7 +13533,7 @@
       <c r="S206" t="inlineStr"/>
       <c r="T206" t="inlineStr">
         <is>
-          <t>lymphatic draining brush for face</t>
+          <t>facial sculpting brush</t>
         </is>
       </c>
       <c r="U206" t="inlineStr"/>
@@ -13604,7 +13594,7 @@
       <c r="S207" t="inlineStr"/>
       <c r="T207" t="inlineStr">
         <is>
-          <t>facial drainage brush</t>
+          <t>soft face brush lymphatic</t>
         </is>
       </c>
       <c r="U207" t="inlineStr"/>
@@ -13665,7 +13655,7 @@
       <c r="S208" t="inlineStr"/>
       <c r="T208" t="inlineStr">
         <is>
-          <t>sculpt brush for face</t>
+          <t>lymphatic drain brush for face</t>
         </is>
       </c>
       <c r="U208" t="inlineStr"/>
@@ -13726,7 +13716,7 @@
       <c r="S209" t="inlineStr"/>
       <c r="T209" t="inlineStr">
         <is>
-          <t>korean face lifting brush</t>
+          <t>facial brushes for lymphatic drainage</t>
         </is>
       </c>
       <c r="U209" t="inlineStr"/>
@@ -13787,7 +13777,7 @@
       <c r="S210" t="inlineStr"/>
       <c r="T210" t="inlineStr">
         <is>
-          <t>facial lymph drainage brush</t>
+          <t>lymphatic draining brush for face</t>
         </is>
       </c>
       <c r="U210" t="inlineStr"/>
@@ -13848,7 +13838,7 @@
       <c r="S211" t="inlineStr"/>
       <c r="T211" t="inlineStr">
         <is>
-          <t>lymphatic facial contour brush</t>
+          <t>facial drainage brush</t>
         </is>
       </c>
       <c r="U211" t="inlineStr"/>
@@ -13909,7 +13899,7 @@
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr">
         <is>
-          <t>sculpting face brush</t>
+          <t>sculpt brush for face</t>
         </is>
       </c>
       <c r="U212" t="inlineStr"/>
@@ -13970,7 +13960,7 @@
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr">
         <is>
-          <t>dry lymphatic massage brush for face</t>
+          <t>korean face lifting brush</t>
         </is>
       </c>
       <c r="U213" t="inlineStr"/>
@@ -14031,7 +14021,7 @@
       <c r="S214" t="inlineStr"/>
       <c r="T214" t="inlineStr">
         <is>
-          <t>lymphatic contour brush for face</t>
+          <t>facial lymph drainage brush</t>
         </is>
       </c>
       <c r="U214" t="inlineStr"/>
@@ -14092,7 +14082,7 @@
       <c r="S215" t="inlineStr"/>
       <c r="T215" t="inlineStr">
         <is>
-          <t>face brush lymphatic drainage</t>
+          <t>lymphatic facial contour brush</t>
         </is>
       </c>
       <c r="U215" t="inlineStr"/>
@@ -14153,7 +14143,7 @@
       <c r="S216" t="inlineStr"/>
       <c r="T216" t="inlineStr">
         <is>
-          <t>facial contour brush</t>
+          <t>sculpting face brush</t>
         </is>
       </c>
       <c r="U216" t="inlineStr"/>
@@ -14214,7 +14204,7 @@
       <c r="S217" t="inlineStr"/>
       <c r="T217" t="inlineStr">
         <is>
-          <t>contour lymphatic face brush</t>
+          <t>dry lymphatic massage brush for face</t>
         </is>
       </c>
       <c r="U217" t="inlineStr"/>
@@ -14275,7 +14265,7 @@
       <c r="S218" t="inlineStr"/>
       <c r="T218" t="inlineStr">
         <is>
-          <t>dry brush face</t>
+          <t>lymphatic contour brush for face</t>
         </is>
       </c>
       <c r="U218" t="inlineStr"/>
@@ -14336,7 +14326,7 @@
       <c r="S219" t="inlineStr"/>
       <c r="T219" t="inlineStr">
         <is>
-          <t>face lymphatic brush</t>
+          <t>face brush lymphatic drainage</t>
         </is>
       </c>
       <c r="U219" t="inlineStr"/>
@@ -14397,7 +14387,7 @@
       <c r="S220" t="inlineStr"/>
       <c r="T220" t="inlineStr">
         <is>
-          <t>korean brush for face</t>
+          <t>facial contour brush</t>
         </is>
       </c>
       <c r="U220" t="inlineStr"/>
@@ -14458,7 +14448,7 @@
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr">
         <is>
-          <t>face lymphatic contour brush</t>
+          <t>contour lymphatic face brush</t>
         </is>
       </c>
       <c r="U221" t="inlineStr"/>
@@ -14519,7 +14509,7 @@
       <c r="S222" t="inlineStr"/>
       <c r="T222" t="inlineStr">
         <is>
-          <t>face massage brush</t>
+          <t>dry brush face</t>
         </is>
       </c>
       <c r="U222" t="inlineStr"/>
@@ -14580,7 +14570,7 @@
       <c r="S223" t="inlineStr"/>
       <c r="T223" t="inlineStr">
         <is>
-          <t>dry brush for lymphatic drainage face</t>
+          <t>face lymphatic brush</t>
         </is>
       </c>
       <c r="U223" t="inlineStr"/>
@@ -14641,7 +14631,7 @@
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr">
         <is>
-          <t>face lifting brush</t>
+          <t>korean brush for face</t>
         </is>
       </c>
       <c r="U224" t="inlineStr"/>
@@ -14702,7 +14692,7 @@
       <c r="S225" t="inlineStr"/>
       <c r="T225" t="inlineStr">
         <is>
-          <t>depuff brush for face</t>
+          <t>face lymphatic contour brush</t>
         </is>
       </c>
       <c r="U225" t="inlineStr"/>
@@ -14763,7 +14753,7 @@
       <c r="S226" t="inlineStr"/>
       <c r="T226" t="inlineStr">
         <is>
-          <t>face dry brush for lymphatic drainage</t>
+          <t>face massage brush</t>
         </is>
       </c>
       <c r="U226" t="inlineStr"/>
@@ -14824,7 +14814,7 @@
       <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr">
         <is>
-          <t>korean lymphatic face brush</t>
+          <t>dry brush for lymphatic drainage face</t>
         </is>
       </c>
       <c r="U227" t="inlineStr"/>
@@ -14885,7 +14875,7 @@
       <c r="S228" t="inlineStr"/>
       <c r="T228" t="inlineStr">
         <is>
-          <t>contour glow brush for face</t>
+          <t>face lifting brush</t>
         </is>
       </c>
       <c r="U228" t="inlineStr"/>
@@ -14946,7 +14936,7 @@
       <c r="S229" t="inlineStr"/>
       <c r="T229" t="inlineStr">
         <is>
-          <t>k glow face sculpting brush</t>
+          <t>depuff brush for face</t>
         </is>
       </c>
       <c r="U229" t="inlineStr"/>
@@ -15007,7 +14997,7 @@
       <c r="S230" t="inlineStr"/>
       <c r="T230" t="inlineStr">
         <is>
-          <t>contour glow brush</t>
+          <t>face dry brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U230" t="inlineStr"/>
@@ -15068,7 +15058,7 @@
       <c r="S231" t="inlineStr"/>
       <c r="T231" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush k glow</t>
+          <t>korean lymphatic face brush</t>
         </is>
       </c>
       <c r="U231" t="inlineStr"/>
@@ -15129,7 +15119,7 @@
       <c r="S232" t="inlineStr"/>
       <c r="T232" t="inlineStr">
         <is>
-          <t>contour glow face brush</t>
+          <t>contour glow brush for face</t>
         </is>
       </c>
       <c r="U232" t="inlineStr"/>
@@ -15190,7 +15180,7 @@
       <c r="S233" t="inlineStr"/>
       <c r="T233" t="inlineStr">
         <is>
-          <t>contourglow brush</t>
+          <t>k glow face sculpting brush</t>
         </is>
       </c>
       <c r="U233" t="inlineStr"/>
@@ -15251,7 +15241,7 @@
       <c r="S234" t="inlineStr"/>
       <c r="T234" t="inlineStr">
         <is>
-          <t>skinn double-ended face massage brush</t>
+          <t>contour glow brush</t>
         </is>
       </c>
       <c r="U234" t="inlineStr"/>
@@ -15312,7 +15302,7 @@
       <c r="S235" t="inlineStr"/>
       <c r="T235" t="inlineStr">
         <is>
-          <t>nuventra facial brush</t>
+          <t>lymphatic contour face brush k glow</t>
         </is>
       </c>
       <c r="U235" t="inlineStr"/>
@@ -15373,7 +15363,7 @@
       <c r="S236" t="inlineStr"/>
       <c r="T236" t="inlineStr">
         <is>
-          <t>face beauty workshop lymphatic brush</t>
+          <t>contour glow face brush</t>
         </is>
       </c>
       <c r="U236" t="inlineStr"/>
@@ -15434,7 +15424,7 @@
       <c r="S237" t="inlineStr"/>
       <c r="T237" t="inlineStr">
         <is>
-          <t>koneva lymphatic face brush</t>
+          <t>contourglow brush</t>
         </is>
       </c>
       <c r="U237" t="inlineStr"/>
@@ -15495,7 +15485,7 @@
       <c r="S238" t="inlineStr"/>
       <c r="T238" t="inlineStr">
         <is>
-          <t>floriem lymphatic face brush</t>
+          <t>skinn double-ended face massage brush</t>
         </is>
       </c>
       <c r="U238" t="inlineStr"/>
@@ -15556,7 +15546,7 @@
       <c r="S239" t="inlineStr"/>
       <c r="T239" t="inlineStr">
         <is>
-          <t>auvorra lymphatic contour face brush</t>
+          <t>nuventra facial brush</t>
         </is>
       </c>
       <c r="U239" t="inlineStr"/>
@@ -15617,7 +15607,7 @@
       <c r="S240" t="inlineStr"/>
       <c r="T240" t="inlineStr">
         <is>
-          <t>kojeca lymphatic face brush</t>
+          <t>face beauty workshop lymphatic brush</t>
         </is>
       </c>
       <c r="U240" t="inlineStr"/>
@@ -15678,7 +15668,7 @@
       <c r="S241" t="inlineStr"/>
       <c r="T241" t="inlineStr">
         <is>
-          <t>nuevetra face brush</t>
+          <t>koneva lymphatic face brush</t>
         </is>
       </c>
       <c r="U241" t="inlineStr"/>
@@ -15739,7 +15729,7 @@
       <c r="S242" t="inlineStr"/>
       <c r="T242" t="inlineStr">
         <is>
-          <t>kogeva lymphatic face brush</t>
+          <t>floriem lymphatic face brush</t>
         </is>
       </c>
       <c r="U242" t="inlineStr"/>
@@ -15800,7 +15790,7 @@
       <c r="S243" t="inlineStr"/>
       <c r="T243" t="inlineStr">
         <is>
-          <t>cecily braden lymphatic face brush</t>
+          <t>auvorra lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U243" t="inlineStr"/>
@@ -15861,7 +15851,7 @@
       <c r="S244" t="inlineStr"/>
       <c r="T244" t="inlineStr">
         <is>
-          <t>soothesilk facial contour brush</t>
+          <t>kojeca lymphatic face brush</t>
         </is>
       </c>
       <c r="U244" t="inlineStr"/>
@@ -15922,7 +15912,7 @@
       <c r="S245" t="inlineStr"/>
       <c r="T245" t="inlineStr">
         <is>
-          <t>sefvako lymphatic contour face brush</t>
+          <t>nuevetra face brush</t>
         </is>
       </c>
       <c r="U245" t="inlineStr"/>
@@ -15983,7 +15973,7 @@
       <c r="S246" t="inlineStr"/>
       <c r="T246" t="inlineStr">
         <is>
-          <t>recuvia lymphatic contour face brush eliminate puffiness in minutes</t>
+          <t>kogeva lymphatic face brush</t>
         </is>
       </c>
       <c r="U246" t="inlineStr"/>
@@ -16044,7 +16034,7 @@
       <c r="S247" t="inlineStr"/>
       <c r="T247" t="inlineStr">
         <is>
-          <t>vough lymphatic contour face brush</t>
+          <t>cecily braden lymphatic face brush</t>
         </is>
       </c>
       <c r="U247" t="inlineStr"/>
@@ -16105,7 +16095,7 @@
       <c r="S248" t="inlineStr"/>
       <c r="T248" t="inlineStr">
         <is>
-          <t>akei lymphatic facial brush</t>
+          <t>soothesilk facial contour brush</t>
         </is>
       </c>
       <c r="U248" t="inlineStr"/>
@@ -16166,7 +16156,7 @@
       <c r="S249" t="inlineStr"/>
       <c r="T249" t="inlineStr">
         <is>
-          <t>aeli lymphatic face brush</t>
+          <t>sefvako lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U249" t="inlineStr"/>
@@ -16227,7 +16217,7 @@
       <c r="S250" t="inlineStr"/>
       <c r="T250" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush puur house</t>
+          <t>recuvia lymphatic contour face brush eliminate puffiness in minutes</t>
         </is>
       </c>
       <c r="U250" t="inlineStr"/>
@@ -16288,7 +16278,7 @@
       <c r="S251" t="inlineStr"/>
       <c r="T251" t="inlineStr">
         <is>
-          <t>koje a lymphatic face brush</t>
+          <t>vough lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U251" t="inlineStr"/>
@@ -16349,7 +16339,7 @@
       <c r="S252" t="inlineStr"/>
       <c r="T252" t="inlineStr">
         <is>
-          <t>koheva lymphatic face brush</t>
+          <t>akei lymphatic facial brush</t>
         </is>
       </c>
       <c r="U252" t="inlineStr"/>
@@ -16410,7 +16400,7 @@
       <c r="S253" t="inlineStr"/>
       <c r="T253" t="inlineStr">
         <is>
-          <t>awki lymphatic face brush</t>
+          <t>aeli lymphatic face brush</t>
         </is>
       </c>
       <c r="U253" t="inlineStr"/>
@@ -16471,7 +16461,7 @@
       <c r="S254" t="inlineStr"/>
       <c r="T254" t="inlineStr">
         <is>
-          <t>kojovia face brush for lymphatic drainage</t>
+          <t>lymphatic contour face brush puur house</t>
         </is>
       </c>
       <c r="U254" t="inlineStr"/>
@@ -16532,7 +16522,7 @@
       <c r="S255" t="inlineStr"/>
       <c r="T255" t="inlineStr">
         <is>
-          <t>arki lymphatic face brush</t>
+          <t>koje a lymphatic face brush</t>
         </is>
       </c>
       <c r="U255" t="inlineStr"/>
@@ -16593,7 +16583,7 @@
       <c r="S256" t="inlineStr"/>
       <c r="T256" t="inlineStr">
         <is>
-          <t>puur house lymphatic contour face brush</t>
+          <t>koheva lymphatic face brush</t>
         </is>
       </c>
       <c r="U256" t="inlineStr"/>
@@ -16654,7 +16644,7 @@
       <c r="S257" t="inlineStr"/>
       <c r="T257" t="inlineStr">
         <is>
-          <t>lymphatic brush by cecily braden</t>
+          <t>awki lymphatic face brush</t>
         </is>
       </c>
       <c r="U257" t="inlineStr"/>
@@ -16715,7 +16705,7 @@
       <c r="S258" t="inlineStr"/>
       <c r="T258" t="inlineStr">
         <is>
-          <t>kojevs lymphatic face brush</t>
+          <t>kojovia face brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U258" t="inlineStr"/>
@@ -16776,7 +16766,7 @@
       <c r="S259" t="inlineStr"/>
       <c r="T259" t="inlineStr">
         <is>
-          <t>eteross lymphatic face brush</t>
+          <t>arki lymphatic face brush</t>
         </is>
       </c>
       <c r="U259" t="inlineStr"/>
@@ -16837,7 +16827,7 @@
       <c r="S260" t="inlineStr"/>
       <c r="T260" t="inlineStr">
         <is>
-          <t>vddo lymphatic contour face brush</t>
+          <t>puur house lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U260" t="inlineStr"/>
@@ -16898,7 +16888,7 @@
       <c r="S261" t="inlineStr"/>
       <c r="T261" t="inlineStr">
         <is>
-          <t>vellorra lymphatic contour face brush</t>
+          <t>lymphatic brush by cecily braden</t>
         </is>
       </c>
       <c r="U261" t="inlineStr"/>
@@ -16959,7 +16949,7 @@
       <c r="S262" t="inlineStr"/>
       <c r="T262" t="inlineStr">
         <is>
-          <t>lymphatic contour face brush</t>
+          <t>kojevs lymphatic face brush</t>
         </is>
       </c>
       <c r="U262" t="inlineStr"/>
@@ -17020,7 +17010,7 @@
       <c r="S263" t="inlineStr"/>
       <c r="T263" t="inlineStr">
         <is>
-          <t>glow brush lymphatic</t>
+          <t>eteross lymphatic face brush</t>
         </is>
       </c>
       <c r="U263" t="inlineStr"/>
@@ -17081,7 +17071,7 @@
       <c r="S264" t="inlineStr"/>
       <c r="T264" t="inlineStr">
         <is>
-          <t>korean lymphatic brush</t>
+          <t>vddo lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U264" t="inlineStr"/>
@@ -17142,7 +17132,7 @@
       <c r="S265" t="inlineStr"/>
       <c r="T265" t="inlineStr">
         <is>
-          <t>glow brush for face</t>
+          <t>vellorra lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U265" t="inlineStr"/>
@@ -17203,7 +17193,7 @@
       <c r="S266" t="inlineStr"/>
       <c r="T266" t="inlineStr">
         <is>
-          <t>counter glow face brush</t>
+          <t>lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U266" t="inlineStr"/>
@@ -17264,7 +17254,7 @@
       <c r="S267" t="inlineStr"/>
       <c r="T267" t="inlineStr">
         <is>
-          <t>counterglow face brush</t>
+          <t>glow brush lymphatic</t>
         </is>
       </c>
       <c r="U267" t="inlineStr"/>
@@ -17325,7 +17315,7 @@
       <c r="S268" t="inlineStr"/>
       <c r="T268" t="inlineStr">
         <is>
-          <t>face massager brush</t>
+          <t>korean lymphatic brush</t>
         </is>
       </c>
       <c r="U268" t="inlineStr"/>
@@ -17386,7 +17376,7 @@
       <c r="S269" t="inlineStr"/>
       <c r="T269" t="inlineStr">
         <is>
-          <t>contour face brush for lymphatic drainage</t>
+          <t>glow brush for face</t>
         </is>
       </c>
       <c r="U269" t="inlineStr"/>
@@ -17447,7 +17437,7 @@
       <c r="S270" t="inlineStr"/>
       <c r="T270" t="inlineStr">
         <is>
-          <t>lymphatic drainage face brush</t>
+          <t>counter glow face brush</t>
         </is>
       </c>
       <c r="U270" t="inlineStr"/>
@@ -17508,7 +17498,7 @@
       <c r="S271" t="inlineStr"/>
       <c r="T271" t="inlineStr">
         <is>
-          <t>lymph brush for face and neck</t>
+          <t>counterglow face brush</t>
         </is>
       </c>
       <c r="U271" t="inlineStr"/>
@@ -17569,7 +17559,7 @@
       <c r="S272" t="inlineStr"/>
       <c r="T272" t="inlineStr">
         <is>
-          <t>face brush for lymphatic drainage</t>
+          <t>face massager brush</t>
         </is>
       </c>
       <c r="U272" t="inlineStr"/>
@@ -17630,7 +17620,7 @@
       <c r="S273" t="inlineStr"/>
       <c r="T273" t="inlineStr">
         <is>
-          <t>soft bristle face brush</t>
+          <t>contour face brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U273" t="inlineStr"/>
@@ -17691,7 +17681,7 @@
       <c r="S274" t="inlineStr"/>
       <c r="T274" t="inlineStr">
         <is>
-          <t>lymphatic dry brush for face</t>
+          <t>lymphatic drainage face brush</t>
         </is>
       </c>
       <c r="U274" t="inlineStr"/>
@@ -17752,7 +17742,7 @@
       <c r="S275" t="inlineStr"/>
       <c r="T275" t="inlineStr">
         <is>
-          <t>face sculpting brush lymphatic</t>
+          <t>lymph brush for face and neck</t>
         </is>
       </c>
       <c r="U275" t="inlineStr"/>
@@ -17813,7 +17803,7 @@
       <c r="S276" t="inlineStr"/>
       <c r="T276" t="inlineStr">
         <is>
-          <t>nuvetra contour glow brush</t>
+          <t>face brush for lymphatic drainage</t>
         </is>
       </c>
       <c r="U276" t="inlineStr"/>
@@ -17874,7 +17864,7 @@
       <c r="S277" t="inlineStr"/>
       <c r="T277" t="inlineStr">
         <is>
-          <t>kojeva lymphatic brush face</t>
+          <t>soft bristle face brush</t>
         </is>
       </c>
       <c r="U277" t="inlineStr"/>
@@ -17935,7 +17925,7 @@
       <c r="S278" t="inlineStr"/>
       <c r="T278" t="inlineStr">
         <is>
-          <t>akei lymphatic brush</t>
+          <t>lymphatic dry brush for face</t>
         </is>
       </c>
       <c r="U278" t="inlineStr"/>
@@ -17996,7 +17986,7 @@
       <c r="S279" t="inlineStr"/>
       <c r="T279" t="inlineStr">
         <is>
-          <t>koniva face brush</t>
+          <t>face sculpting brush lymphatic</t>
         </is>
       </c>
       <c r="U279" t="inlineStr"/>
@@ -18057,7 +18047,7 @@
       <c r="S280" t="inlineStr"/>
       <c r="T280" t="inlineStr">
         <is>
-          <t>soothesilk facial brush</t>
+          <t>nuvetra contour glow brush</t>
         </is>
       </c>
       <c r="U280" t="inlineStr"/>
@@ -18118,7 +18108,7 @@
       <c r="S281" t="inlineStr"/>
       <c r="T281" t="inlineStr">
         <is>
-          <t>gua sha facial tools</t>
+          <t>kojeva lymphatic brush face</t>
         </is>
       </c>
       <c r="U281" t="inlineStr"/>
@@ -18179,7 +18169,7 @@
       <c r="S282" t="inlineStr"/>
       <c r="T282" t="inlineStr">
         <is>
-          <t>kojeva lymphatic face brush</t>
+          <t>akei lymphatic brush</t>
         </is>
       </c>
       <c r="U282" t="inlineStr"/>
@@ -18240,7 +18230,7 @@
       <c r="S283" t="inlineStr"/>
       <c r="T283" t="inlineStr">
         <is>
-          <t>kitsch lymphatic contour face brush</t>
+          <t>koniva face brush</t>
         </is>
       </c>
       <c r="U283" t="inlineStr"/>
@@ -18301,7 +18291,7 @@
       <c r="S284" t="inlineStr"/>
       <c r="T284" t="inlineStr">
         <is>
-          <t>facial brush</t>
+          <t>soothesilk facial brush</t>
         </is>
       </c>
       <c r="U284" t="inlineStr"/>
@@ -18362,7 +18352,7 @@
       <c r="S285" t="inlineStr"/>
       <c r="T285" t="inlineStr">
         <is>
-          <t>guasha tool for face</t>
+          <t>gua sha facial tools</t>
         </is>
       </c>
       <c r="U285" t="inlineStr"/>
@@ -18423,7 +18413,7 @@
       <c r="S286" t="inlineStr"/>
       <c r="T286" t="inlineStr">
         <is>
-          <t>contour brush</t>
+          <t>kojeva lymphatic face brush</t>
         </is>
       </c>
       <c r="U286" t="inlineStr"/>
@@ -18484,7 +18474,7 @@
       <c r="S287" t="inlineStr"/>
       <c r="T287" t="inlineStr">
         <is>
-          <t>face mask brush</t>
+          <t>kitsch lymphatic contour face brush</t>
         </is>
       </c>
       <c r="U287" t="inlineStr"/>
@@ -18545,14 +18535,14 @@
       <c r="S288" t="inlineStr"/>
       <c r="T288" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>facial brush</t>
         </is>
       </c>
       <c r="U288" t="inlineStr"/>
       <c r="V288" t="inlineStr"/>
       <c r="W288" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
       <c r="X288" t="inlineStr"/>
@@ -18606,14 +18596,14 @@
       <c r="S289" t="inlineStr"/>
       <c r="T289" t="inlineStr">
         <is>
-          <t>makeup</t>
+          <t>guasha tool for face</t>
         </is>
       </c>
       <c r="U289" t="inlineStr"/>
       <c r="V289" t="inlineStr"/>
       <c r="W289" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
       <c r="X289" t="inlineStr"/>
@@ -18667,14 +18657,14 @@
       <c r="S290" t="inlineStr"/>
       <c r="T290" t="inlineStr">
         <is>
-          <t>body</t>
+          <t>contour brush</t>
         </is>
       </c>
       <c r="U290" t="inlineStr"/>
       <c r="V290" t="inlineStr"/>
       <c r="W290" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
       <c r="X290" t="inlineStr"/>
@@ -18728,14 +18718,14 @@
       <c r="S291" t="inlineStr"/>
       <c r="T291" t="inlineStr">
         <is>
-          <t>drops</t>
+          <t>face mask brush</t>
         </is>
       </c>
       <c r="U291" t="inlineStr"/>
       <c r="V291" t="inlineStr"/>
       <c r="W291" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
       <c r="X291" t="inlineStr"/>
@@ -18789,7 +18779,7 @@
       <c r="S292" t="inlineStr"/>
       <c r="T292" t="inlineStr">
         <is>
-          <t>supplement</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="U292" t="inlineStr"/>
@@ -18850,7 +18840,7 @@
       <c r="S293" t="inlineStr"/>
       <c r="T293" t="inlineStr">
         <is>
-          <t>pills</t>
+          <t>makeup</t>
         </is>
       </c>
       <c r="U293" t="inlineStr"/>
@@ -18911,7 +18901,7 @@
       <c r="S294" t="inlineStr"/>
       <c r="T294" t="inlineStr">
         <is>
-          <t>toothbrush</t>
+          <t>body</t>
         </is>
       </c>
       <c r="U294" t="inlineStr"/>
@@ -18972,7 +18962,7 @@
       <c r="S295" t="inlineStr"/>
       <c r="T295" t="inlineStr">
         <is>
-          <t>cleansing</t>
+          <t>drops</t>
         </is>
       </c>
       <c r="U295" t="inlineStr"/>
@@ -19033,7 +19023,7 @@
       <c r="S296" t="inlineStr"/>
       <c r="T296" t="inlineStr">
         <is>
-          <t>exfoliating</t>
+          <t>supplement</t>
         </is>
       </c>
       <c r="U296" t="inlineStr"/>
@@ -19094,7 +19084,7 @@
       <c r="S297" t="inlineStr"/>
       <c r="T297" t="inlineStr">
         <is>
-          <t>powder</t>
+          <t>pills</t>
         </is>
       </c>
       <c r="U297" t="inlineStr"/>
@@ -19155,7 +19145,7 @@
       <c r="S298" t="inlineStr"/>
       <c r="T298" t="inlineStr">
         <is>
-          <t>ice roller</t>
+          <t>toothbrush</t>
         </is>
       </c>
       <c r="U298" t="inlineStr"/>
@@ -19216,7 +19206,7 @@
       <c r="S299" t="inlineStr"/>
       <c r="T299" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>cleansing</t>
         </is>
       </c>
       <c r="U299" t="inlineStr"/>
@@ -19277,7 +19267,7 @@
       <c r="S300" t="inlineStr"/>
       <c r="T300" t="inlineStr">
         <is>
-          <t>peel</t>
+          <t>exfoliating</t>
         </is>
       </c>
       <c r="U300" t="inlineStr"/>
@@ -19300,7 +19290,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Negative Product Targeting</t>
+          <t>Negative Keyword</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -19336,18 +19326,22 @@
       <c r="Q301" t="inlineStr"/>
       <c r="R301" t="inlineStr"/>
       <c r="S301" t="inlineStr"/>
-      <c r="T301" t="inlineStr"/>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>powder</t>
+        </is>
+      </c>
       <c r="U301" t="inlineStr"/>
       <c r="V301" t="inlineStr"/>
-      <c r="W301" t="inlineStr"/>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
       <c r="X301" t="inlineStr"/>
       <c r="Y301" t="inlineStr"/>
       <c r="Z301" t="inlineStr"/>
-      <c r="AA301" t="inlineStr">
-        <is>
-          <t>asin="B0FD354L27"</t>
-        </is>
-      </c>
+      <c r="AA301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -19357,7 +19351,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Negative Product Targeting</t>
+          <t>Negative Keyword</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -19393,14 +19387,254 @@
       <c r="Q302" t="inlineStr"/>
       <c r="R302" t="inlineStr"/>
       <c r="S302" t="inlineStr"/>
-      <c r="T302" t="inlineStr"/>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>ice roller</t>
+        </is>
+      </c>
       <c r="U302" t="inlineStr"/>
       <c r="V302" t="inlineStr"/>
-      <c r="W302" t="inlineStr"/>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
       <c r="X302" t="inlineStr"/>
       <c r="Y302" t="inlineStr"/>
       <c r="Z302" t="inlineStr"/>
-      <c r="AA302" t="inlineStr">
+      <c r="AA302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
+      <c r="J303" t="inlineStr"/>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr"/>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr"/>
+      <c r="Q303" t="inlineStr"/>
+      <c r="R303" t="inlineStr"/>
+      <c r="S303" t="inlineStr"/>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>foundation</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr"/>
+      <c r="V303" t="inlineStr"/>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+      <c r="X303" t="inlineStr"/>
+      <c r="Y303" t="inlineStr"/>
+      <c r="Z303" t="inlineStr"/>
+      <c r="AA303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Negative Keyword</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
+      <c r="J304" t="inlineStr"/>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr"/>
+      <c r="Q304" t="inlineStr"/>
+      <c r="R304" t="inlineStr"/>
+      <c r="S304" t="inlineStr"/>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>peel</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr"/>
+      <c r="V304" t="inlineStr"/>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t>negativePhrase</t>
+        </is>
+      </c>
+      <c r="X304" t="inlineStr"/>
+      <c r="Y304" t="inlineStr"/>
+      <c r="Z304" t="inlineStr"/>
+      <c r="AA304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Negative Product Targeting</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
+      <c r="J305" t="inlineStr"/>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr"/>
+      <c r="Q305" t="inlineStr"/>
+      <c r="R305" t="inlineStr"/>
+      <c r="S305" t="inlineStr"/>
+      <c r="T305" t="inlineStr"/>
+      <c r="U305" t="inlineStr"/>
+      <c r="V305" t="inlineStr"/>
+      <c r="W305" t="inlineStr"/>
+      <c r="X305" t="inlineStr"/>
+      <c r="Y305" t="inlineStr"/>
+      <c r="Z305" t="inlineStr"/>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>asin="B0FD354L27"</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Negative Product Targeting</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>AVIE_OCT_AUTO_COSECHA</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>avie_oct_auto_cosecha</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
+      <c r="J306" t="inlineStr"/>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr"/>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr"/>
+      <c r="Q306" t="inlineStr"/>
+      <c r="R306" t="inlineStr"/>
+      <c r="S306" t="inlineStr"/>
+      <c r="T306" t="inlineStr"/>
+      <c r="U306" t="inlineStr"/>
+      <c r="V306" t="inlineStr"/>
+      <c r="W306" t="inlineStr"/>
+      <c r="X306" t="inlineStr"/>
+      <c r="Y306" t="inlineStr"/>
+      <c r="Z306" t="inlineStr"/>
+      <c r="AA306" t="inlineStr">
         <is>
           <t>asin="B0FD6Y9BX5"</t>
         </is>
